--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4357,10 +4357,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121263003</v>
+        <v>121262997</v>
       </c>
       <c r="B33" t="n">
-        <v>57364</v>
+        <v>78802</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4369,39 +4369,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>1639</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4463,6 +4454,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4481,10 +4473,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121262997</v>
+        <v>121263003</v>
       </c>
       <c r="B34" t="n">
-        <v>78799</v>
+        <v>57367</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4493,30 +4485,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1639</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4578,7 +4579,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4357,10 +4357,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121262997</v>
+        <v>121263003</v>
       </c>
       <c r="B33" t="n">
-        <v>78802</v>
+        <v>57367</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4369,30 +4369,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1639</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4454,7 +4463,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4473,10 +4481,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121263003</v>
+        <v>121262997</v>
       </c>
       <c r="B34" t="n">
-        <v>57367</v>
+        <v>78802</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4485,39 +4493,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1639</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4579,6 +4578,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4357,10 +4357,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121263003</v>
+        <v>121262997</v>
       </c>
       <c r="B33" t="n">
-        <v>57367</v>
+        <v>78805</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4369,39 +4369,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>1639</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4463,6 +4454,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4481,10 +4473,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121262997</v>
+        <v>121263003</v>
       </c>
       <c r="B34" t="n">
-        <v>78802</v>
+        <v>57367</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4493,30 +4485,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1639</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4578,7 +4579,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4466,7 +4466,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Brenander, Florian Bossert</t>
+          <t>Florian Bossert, Jan Brenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jan Brenander, Florian Bossert</t>
+          <t>Florian Bossert, Jan Brenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4360,7 +4360,7 @@
         <v>121262997</v>
       </c>
       <c r="B33" t="n">
-        <v>78805</v>
+        <v>78808</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Florian Bossert, Jan Brenander</t>
+          <t>Jan Brenander, Florian Bossert</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4476,7 +4476,7 @@
         <v>121263003</v>
       </c>
       <c r="B34" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Florian Bossert, Jan Brenander</t>
+          <t>Jan Brenander, Florian Bossert</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4357,10 +4357,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121262997</v>
+        <v>121263003</v>
       </c>
       <c r="B33" t="n">
-        <v>78808</v>
+        <v>57370</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4369,30 +4369,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1639</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4454,7 +4463,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4473,10 +4481,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121263003</v>
+        <v>121262997</v>
       </c>
       <c r="B34" t="n">
-        <v>57370</v>
+        <v>78808</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4485,39 +4493,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1639</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4579,6 +4578,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4360,7 +4360,7 @@
         <v>121263003</v>
       </c>
       <c r="B33" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>121262997</v>
       </c>
       <c r="B34" t="n">
-        <v>78808</v>
+        <v>78809</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4360,7 +4360,7 @@
         <v>121263003</v>
       </c>
       <c r="B33" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>121262997</v>
       </c>
       <c r="B34" t="n">
-        <v>78809</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4357,10 +4357,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121263003</v>
+        <v>121262997</v>
       </c>
       <c r="B33" t="n">
-        <v>57372</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4369,39 +4369,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>1639</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4463,6 +4454,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4481,10 +4473,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121262997</v>
+        <v>121263003</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>57372</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4493,30 +4485,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1639</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4578,7 +4579,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4466,7 +4466,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Brenander, Florian Bossert</t>
+          <t>Florian Bossert, Jan Brenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4597,10 +4597,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124303500</v>
+        <v>124305419</v>
       </c>
       <c r="B35" t="n">
-        <v>56722</v>
+        <v>95423</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4613,46 +4613,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>2671</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578140</v>
+        <v>577961</v>
       </c>
       <c r="R35" t="n">
-        <v>6340418</v>
+        <v>6340362</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4708,10 +4699,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124304453</v>
+        <v>124307670</v>
       </c>
       <c r="B36" t="n">
-        <v>57529</v>
+        <v>95423</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4720,25 +4711,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>2671</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4748,13 +4739,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578088</v>
+        <v>578089</v>
       </c>
       <c r="R36" t="n">
-        <v>6340470</v>
+        <v>6340417</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4784,11 +4775,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4815,10 +4801,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124306409</v>
+        <v>124304628</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>95705</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4827,25 +4813,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4855,13 +4841,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577906</v>
+        <v>578054</v>
       </c>
       <c r="R37" t="n">
-        <v>6340336</v>
+        <v>6340399</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4917,10 +4903,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124306142</v>
+        <v>124303500</v>
       </c>
       <c r="B38" t="n">
-        <v>95705</v>
+        <v>56722</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4933,37 +4919,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577937</v>
+        <v>578140</v>
       </c>
       <c r="R38" t="n">
-        <v>6340345</v>
+        <v>6340418</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5121,10 +5116,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124304628</v>
+        <v>124308072</v>
       </c>
       <c r="B40" t="n">
-        <v>95705</v>
+        <v>105117</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5137,21 +5132,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5161,13 +5156,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578054</v>
+        <v>578059</v>
       </c>
       <c r="R40" t="n">
-        <v>6340399</v>
+        <v>6340412</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5223,10 +5218,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124305419</v>
+        <v>124304453</v>
       </c>
       <c r="B41" t="n">
-        <v>95423</v>
+        <v>57529</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5235,25 +5230,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2671</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5263,10 +5258,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577961</v>
+        <v>578088</v>
       </c>
       <c r="R41" t="n">
-        <v>6340362</v>
+        <v>6340470</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5299,6 +5294,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5325,10 +5325,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124307670</v>
+        <v>124306409</v>
       </c>
       <c r="B42" t="n">
-        <v>95423</v>
+        <v>91012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5337,25 +5337,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2671</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5365,13 +5365,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578089</v>
+        <v>577906</v>
       </c>
       <c r="R42" t="n">
-        <v>6340417</v>
+        <v>6340336</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5427,10 +5427,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124308072</v>
+        <v>124306142</v>
       </c>
       <c r="B43" t="n">
-        <v>105117</v>
+        <v>95705</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5443,21 +5443,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578059</v>
+        <v>577937</v>
       </c>
       <c r="R43" t="n">
-        <v>6340412</v>
+        <v>6340345</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4597,10 +4597,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124305419</v>
+        <v>124304628</v>
       </c>
       <c r="B35" t="n">
-        <v>95423</v>
+        <v>95705</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2671</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577961</v>
+        <v>578054</v>
       </c>
       <c r="R35" t="n">
-        <v>6340362</v>
+        <v>6340399</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124307670</v>
+        <v>124306142</v>
       </c>
       <c r="B36" t="n">
-        <v>95423</v>
+        <v>95705</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4715,21 +4715,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2671</v>
+        <v>2180</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4739,13 +4739,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578089</v>
+        <v>577937</v>
       </c>
       <c r="R36" t="n">
-        <v>6340417</v>
+        <v>6340345</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4801,10 +4801,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124304628</v>
+        <v>124303500</v>
       </c>
       <c r="B37" t="n">
-        <v>95705</v>
+        <v>56722</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4817,37 +4817,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578054</v>
+        <v>578140</v>
       </c>
       <c r="R37" t="n">
-        <v>6340399</v>
+        <v>6340418</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4903,10 +4912,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124303500</v>
+        <v>124303584</v>
       </c>
       <c r="B38" t="n">
-        <v>56722</v>
+        <v>91032</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4915,50 +4924,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578140</v>
+        <v>578146</v>
       </c>
       <c r="R38" t="n">
-        <v>6340418</v>
+        <v>6340431</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5014,10 +5014,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124303584</v>
+        <v>124305419</v>
       </c>
       <c r="B39" t="n">
-        <v>91032</v>
+        <v>95423</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5026,25 +5026,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578146</v>
+        <v>577961</v>
       </c>
       <c r="R39" t="n">
-        <v>6340431</v>
+        <v>6340362</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124308072</v>
+        <v>124306409</v>
       </c>
       <c r="B40" t="n">
-        <v>105117</v>
+        <v>91012</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5128,25 +5128,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578059</v>
+        <v>577906</v>
       </c>
       <c r="R40" t="n">
-        <v>6340412</v>
+        <v>6340336</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124304453</v>
+        <v>124307670</v>
       </c>
       <c r="B41" t="n">
-        <v>57529</v>
+        <v>95423</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5230,25 +5230,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>2671</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5258,13 +5258,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578088</v>
+        <v>578089</v>
       </c>
       <c r="R41" t="n">
-        <v>6340470</v>
+        <v>6340417</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5294,11 +5294,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5325,10 +5320,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124306409</v>
+        <v>124304453</v>
       </c>
       <c r="B42" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5341,21 +5336,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5365,10 +5360,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577906</v>
+        <v>578088</v>
       </c>
       <c r="R42" t="n">
-        <v>6340336</v>
+        <v>6340470</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5401,6 +5396,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5427,10 +5427,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124306142</v>
+        <v>124308072</v>
       </c>
       <c r="B43" t="n">
-        <v>95705</v>
+        <v>105117</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5443,21 +5443,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577937</v>
+        <v>578059</v>
       </c>
       <c r="R43" t="n">
-        <v>6340345</v>
+        <v>6340412</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4597,10 +4597,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124304628</v>
+        <v>124307670</v>
       </c>
       <c r="B35" t="n">
-        <v>95705</v>
+        <v>95423</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>2671</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578054</v>
+        <v>578089</v>
       </c>
       <c r="R35" t="n">
-        <v>6340399</v>
+        <v>6340417</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124306142</v>
+        <v>124304628</v>
       </c>
       <c r="B36" t="n">
         <v>95705</v>
@@ -4739,13 +4739,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577937</v>
+        <v>578054</v>
       </c>
       <c r="R36" t="n">
-        <v>6340345</v>
+        <v>6340399</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5014,10 +5014,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124305419</v>
+        <v>124304453</v>
       </c>
       <c r="B39" t="n">
-        <v>95423</v>
+        <v>57529</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5026,25 +5026,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2671</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577961</v>
+        <v>578088</v>
       </c>
       <c r="R39" t="n">
-        <v>6340362</v>
+        <v>6340470</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5090,6 +5090,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5116,10 +5121,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124306409</v>
+        <v>124308072</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>105117</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5128,25 +5133,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5156,10 +5161,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577906</v>
+        <v>578059</v>
       </c>
       <c r="R40" t="n">
-        <v>6340336</v>
+        <v>6340412</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5218,10 +5223,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124307670</v>
+        <v>124306142</v>
       </c>
       <c r="B41" t="n">
-        <v>95423</v>
+        <v>95705</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5234,21 +5239,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2671</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5258,13 +5263,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578089</v>
+        <v>577937</v>
       </c>
       <c r="R41" t="n">
-        <v>6340417</v>
+        <v>6340345</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5320,10 +5325,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124304453</v>
+        <v>124306409</v>
       </c>
       <c r="B42" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5336,21 +5341,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5360,10 +5365,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578088</v>
+        <v>577906</v>
       </c>
       <c r="R42" t="n">
-        <v>6340470</v>
+        <v>6340336</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5396,11 +5401,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5427,10 +5427,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124308072</v>
+        <v>124305419</v>
       </c>
       <c r="B43" t="n">
-        <v>105117</v>
+        <v>95423</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5443,21 +5443,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>2671</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578059</v>
+        <v>577961</v>
       </c>
       <c r="R43" t="n">
-        <v>6340412</v>
+        <v>6340362</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5526,6 +5526,2186 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>124796306</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hjortshult, Hjortshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>577987</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6340434</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>124797132</v>
+      </c>
+      <c r="B45" t="n">
+        <v>5196</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gökhult, Gökhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>578099</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6340486</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>124799230</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92210</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2075</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Rutskinn</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Xylobolus frustulatus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Boidin</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hjortshult, Hjortshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>577970</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6340397</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>124796768</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gökhult, Gökhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>578118</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6340459</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>124795668</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91023</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>578042</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6340382</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>124797728</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Gökhult, Gökhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>578047</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6340449</v>
+      </c>
+      <c r="S49" t="n">
+        <v>20</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>124795621</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57995</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Mosse Hjortshult, Boda, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>578049</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6340376</v>
+      </c>
+      <c r="S50" t="n">
+        <v>30</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>124795772</v>
+      </c>
+      <c r="B51" t="n">
+        <v>96354</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>53</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Gökhult, Gökhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>578110</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6340428</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>124797831</v>
+      </c>
+      <c r="B52" t="n">
+        <v>96354</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>53</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Gökhult, Gökhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>578055</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6340450</v>
+      </c>
+      <c r="S52" t="n">
+        <v>20</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>124796529</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hjortshult, Hjortshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>577974</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6340427</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>124796269</v>
+      </c>
+      <c r="B54" t="n">
+        <v>5361</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Gökhult, Gökhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>578107</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6340454</v>
+      </c>
+      <c r="S54" t="n">
+        <v>20</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>124795744</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>578042</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6340428</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>124795874</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79004</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1639</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blomskägglav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Usnea florida</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>578029</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6340450</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>124797648</v>
+      </c>
+      <c r="B57" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Gökhult, Gökhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>578060</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6340459</v>
+      </c>
+      <c r="S57" t="n">
+        <v>20</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Spår och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>124796185</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hjortshult, Hjortshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>578013</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6340449</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>124797764</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Gökhult, Gökhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>578056</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6340468</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>124796245</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79004</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1639</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blomskägglav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Usnea florida</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hjortshult, Hjortshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>577987</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6340434</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>124795887</v>
+      </c>
+      <c r="B61" t="n">
+        <v>96390</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Gökhult, Gökhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>578113</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6340445</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>124796060</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hjortshult, Hjortshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>578034</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6340457</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>124796606</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92239</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>26</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ekskinn</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Aleurocystidiellum disciforme</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(DC.) Boidin &amp; al.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Gökhult, Gökhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>578096</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6340479</v>
+      </c>
+      <c r="S63" t="n">
+        <v>20</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>124796460</v>
+      </c>
+      <c r="B64" t="n">
+        <v>95423</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Gökhult, Gökhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>578092</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6340465</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4597,10 +4597,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124307670</v>
+        <v>124306142</v>
       </c>
       <c r="B35" t="n">
-        <v>95423</v>
+        <v>95705</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2671</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578089</v>
+        <v>577937</v>
       </c>
       <c r="R35" t="n">
-        <v>6340417</v>
+        <v>6340345</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124304628</v>
+        <v>124306409</v>
       </c>
       <c r="B36" t="n">
-        <v>95705</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4711,25 +4711,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4739,13 +4739,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578054</v>
+        <v>577906</v>
       </c>
       <c r="R36" t="n">
-        <v>6340399</v>
+        <v>6340336</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4801,10 +4801,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124303500</v>
+        <v>124304453</v>
       </c>
       <c r="B37" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4813,50 +4813,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578140</v>
+        <v>578088</v>
       </c>
       <c r="R37" t="n">
-        <v>6340418</v>
+        <v>6340470</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4886,6 +4877,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4912,10 +4908,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124303584</v>
+        <v>124305419</v>
       </c>
       <c r="B38" t="n">
-        <v>91032</v>
+        <v>95423</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4924,25 +4920,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4952,10 +4948,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578146</v>
+        <v>577961</v>
       </c>
       <c r="R38" t="n">
-        <v>6340431</v>
+        <v>6340362</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5014,10 +5010,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124304453</v>
+        <v>124304628</v>
       </c>
       <c r="B39" t="n">
-        <v>57529</v>
+        <v>95705</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5026,25 +5022,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5054,13 +5050,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578088</v>
+        <v>578054</v>
       </c>
       <c r="R39" t="n">
-        <v>6340470</v>
+        <v>6340399</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5090,11 +5086,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5121,10 +5112,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124308072</v>
+        <v>124307670</v>
       </c>
       <c r="B40" t="n">
-        <v>105117</v>
+        <v>95423</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5137,21 +5128,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>2671</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5161,13 +5152,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578059</v>
+        <v>578089</v>
       </c>
       <c r="R40" t="n">
-        <v>6340412</v>
+        <v>6340417</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5223,10 +5214,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124306142</v>
+        <v>124308072</v>
       </c>
       <c r="B41" t="n">
-        <v>95705</v>
+        <v>105117</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5239,21 +5230,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5263,10 +5254,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577937</v>
+        <v>578059</v>
       </c>
       <c r="R41" t="n">
-        <v>6340345</v>
+        <v>6340412</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5325,10 +5316,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124306409</v>
+        <v>124303584</v>
       </c>
       <c r="B42" t="n">
-        <v>91012</v>
+        <v>91032</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5341,21 +5332,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5365,10 +5356,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577906</v>
+        <v>578146</v>
       </c>
       <c r="R42" t="n">
-        <v>6340336</v>
+        <v>6340431</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5427,10 +5418,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124305419</v>
+        <v>124303500</v>
       </c>
       <c r="B43" t="n">
-        <v>95423</v>
+        <v>56722</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5443,37 +5434,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2671</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577961</v>
+        <v>578140</v>
       </c>
       <c r="R43" t="n">
-        <v>6340362</v>
+        <v>6340418</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5529,10 +5529,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124796306</v>
+        <v>124797728</v>
       </c>
       <c r="B44" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5545,37 +5545,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577987</v>
+        <v>578047</v>
       </c>
       <c r="R44" t="n">
-        <v>6340434</v>
+        <v>6340449</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5605,6 +5605,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5619,12 +5624,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5731,17 +5736,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124799230</v>
+        <v>124796306</v>
       </c>
       <c r="B46" t="n">
-        <v>92210</v>
+        <v>79428</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5754,21 +5759,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2075</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5778,10 +5783,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577970</v>
+        <v>577987</v>
       </c>
       <c r="R46" t="n">
-        <v>6340397</v>
+        <v>6340434</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5840,10 +5845,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124796768</v>
+        <v>124795874</v>
       </c>
       <c r="B47" t="n">
-        <v>79428</v>
+        <v>79004</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5852,41 +5857,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>1639</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578118</v>
+        <v>578029</v>
       </c>
       <c r="R47" t="n">
-        <v>6340459</v>
+        <v>6340450</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5930,22 +5935,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124795668</v>
+        <v>124799230</v>
       </c>
       <c r="B48" t="n">
-        <v>91023</v>
+        <v>92210</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5954,42 +5959,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1205</v>
+        <v>2075</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Boidin</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578042</v>
+        <v>577970</v>
       </c>
       <c r="R48" t="n">
-        <v>6340382</v>
+        <v>6340397</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6048,10 +6049,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124797728</v>
+        <v>124795744</v>
       </c>
       <c r="B49" t="n">
-        <v>57529</v>
+        <v>79428</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6064,37 +6065,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578047</v>
+        <v>578042</v>
       </c>
       <c r="R49" t="n">
-        <v>6340449</v>
+        <v>6340428</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6124,11 +6125,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6143,12 +6139,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6266,10 +6262,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124795772</v>
+        <v>124797764</v>
       </c>
       <c r="B51" t="n">
-        <v>96354</v>
+        <v>57666</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6282,37 +6278,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578110</v>
+        <v>578056</v>
       </c>
       <c r="R51" t="n">
-        <v>6340428</v>
+        <v>6340468</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6368,7 +6369,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124797831</v>
+        <v>124795772</v>
       </c>
       <c r="B52" t="n">
         <v>96354</v>
@@ -6408,13 +6409,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578055</v>
+        <v>578110</v>
       </c>
       <c r="R52" t="n">
-        <v>6340450</v>
+        <v>6340428</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6470,10 +6471,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124796529</v>
+        <v>124796768</v>
       </c>
       <c r="B53" t="n">
-        <v>79891</v>
+        <v>79428</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6486,37 +6487,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577974</v>
+        <v>578118</v>
       </c>
       <c r="R53" t="n">
-        <v>6340427</v>
+        <v>6340459</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6560,22 +6561,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124796269</v>
+        <v>124797648</v>
       </c>
       <c r="B54" t="n">
-        <v>5361</v>
+        <v>8447</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6584,25 +6585,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>101728</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6612,10 +6613,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578107</v>
+        <v>578060</v>
       </c>
       <c r="R54" t="n">
-        <v>6340454</v>
+        <v>6340459</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6652,7 +6653,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Kläckhål</t>
+          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6679,10 +6680,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124795744</v>
+        <v>124795668</v>
       </c>
       <c r="B55" t="n">
-        <v>79428</v>
+        <v>91023</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6691,38 +6692,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>1205</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
         <v>578042</v>
       </c>
       <c r="R55" t="n">
-        <v>6340428</v>
+        <v>6340382</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6781,10 +6786,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124795874</v>
+        <v>124796060</v>
       </c>
       <c r="B56" t="n">
-        <v>79004</v>
+        <v>79428</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6793,38 +6798,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1639</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578029</v>
+        <v>578034</v>
       </c>
       <c r="R56" t="n">
-        <v>6340450</v>
+        <v>6340457</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6883,10 +6888,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124797648</v>
+        <v>124796245</v>
       </c>
       <c r="B57" t="n">
-        <v>8447</v>
+        <v>79004</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6899,37 +6904,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>1639</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578060</v>
+        <v>577987</v>
       </c>
       <c r="R57" t="n">
-        <v>6340459</v>
+        <v>6340434</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6959,11 +6964,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6978,22 +6978,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124796185</v>
+        <v>124796529</v>
       </c>
       <c r="B58" t="n">
-        <v>79428</v>
+        <v>79891</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7006,21 +7006,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578013</v>
+        <v>577974</v>
       </c>
       <c r="R58" t="n">
-        <v>6340449</v>
+        <v>6340427</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7092,10 +7092,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124797764</v>
+        <v>124797831</v>
       </c>
       <c r="B59" t="n">
-        <v>57666</v>
+        <v>96354</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7108,42 +7108,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578056</v>
+        <v>578055</v>
       </c>
       <c r="R59" t="n">
-        <v>6340468</v>
+        <v>6340450</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7192,17 +7187,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124796245</v>
+        <v>124796460</v>
       </c>
       <c r="B60" t="n">
-        <v>79004</v>
+        <v>95423</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7215,37 +7210,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1639</v>
+        <v>2671</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577987</v>
+        <v>578092</v>
       </c>
       <c r="R60" t="n">
-        <v>6340434</v>
+        <v>6340465</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7289,22 +7284,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124795887</v>
+        <v>124796185</v>
       </c>
       <c r="B61" t="n">
-        <v>96390</v>
+        <v>79428</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7313,41 +7308,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2590</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578113</v>
+        <v>578013</v>
       </c>
       <c r="R61" t="n">
-        <v>6340445</v>
+        <v>6340449</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7391,22 +7386,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124796060</v>
+        <v>124795887</v>
       </c>
       <c r="B62" t="n">
-        <v>79428</v>
+        <v>96390</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7415,41 +7410,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>2590</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578034</v>
+        <v>578113</v>
       </c>
       <c r="R62" t="n">
-        <v>6340457</v>
+        <v>6340445</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7493,22 +7488,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124796606</v>
+        <v>124796269</v>
       </c>
       <c r="B63" t="n">
-        <v>92239</v>
+        <v>5361</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7517,25 +7512,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>26</v>
+        <v>101728</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7545,10 +7540,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578096</v>
+        <v>578107</v>
       </c>
       <c r="R63" t="n">
-        <v>6340479</v>
+        <v>6340454</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7583,6 +7578,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7600,17 +7600,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124796460</v>
+        <v>124796606</v>
       </c>
       <c r="B64" t="n">
-        <v>95423</v>
+        <v>92239</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7623,21 +7623,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2671</v>
+        <v>26</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7647,13 +7647,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578092</v>
+        <v>578096</v>
       </c>
       <c r="R64" t="n">
-        <v>6340465</v>
+        <v>6340479</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7702,10 +7702,336 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
+          <t>Erland Lindblad, Gunnar Westling</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>124825657</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92210</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2075</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Rutskinn</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Xylobolus frustulatus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Boidin</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Stensjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>577974</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6340399</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY64" t="inlineStr"/>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>124825677</v>
+      </c>
+      <c r="B66" t="n">
+        <v>96390</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Stensjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>578131</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6340387</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>124825691</v>
+      </c>
+      <c r="B67" t="n">
+        <v>4772</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Stensjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>578135</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6340398</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4699,10 +4699,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124306409</v>
+        <v>124303500</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4711,41 +4711,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577906</v>
+        <v>578140</v>
       </c>
       <c r="R36" t="n">
-        <v>6340336</v>
+        <v>6340418</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4801,10 +4810,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124304453</v>
+        <v>124307670</v>
       </c>
       <c r="B37" t="n">
-        <v>57529</v>
+        <v>95423</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4813,25 +4822,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>2671</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4841,13 +4850,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578088</v>
+        <v>578089</v>
       </c>
       <c r="R37" t="n">
-        <v>6340470</v>
+        <v>6340417</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4877,11 +4886,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4908,10 +4912,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124305419</v>
+        <v>124304628</v>
       </c>
       <c r="B38" t="n">
-        <v>95423</v>
+        <v>95705</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4924,21 +4928,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2671</v>
+        <v>2180</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4948,13 +4952,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577961</v>
+        <v>578054</v>
       </c>
       <c r="R38" t="n">
-        <v>6340362</v>
+        <v>6340399</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5010,10 +5014,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124304628</v>
+        <v>124305419</v>
       </c>
       <c r="B39" t="n">
-        <v>95705</v>
+        <v>95423</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5026,21 +5030,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2180</v>
+        <v>2671</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5050,13 +5054,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578054</v>
+        <v>577961</v>
       </c>
       <c r="R39" t="n">
-        <v>6340399</v>
+        <v>6340362</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5112,10 +5116,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124307670</v>
+        <v>124308072</v>
       </c>
       <c r="B40" t="n">
-        <v>95423</v>
+        <v>105117</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5128,21 +5132,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2671</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5152,13 +5156,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578089</v>
+        <v>578059</v>
       </c>
       <c r="R40" t="n">
-        <v>6340417</v>
+        <v>6340412</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5214,10 +5218,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124308072</v>
+        <v>124306409</v>
       </c>
       <c r="B41" t="n">
-        <v>105117</v>
+        <v>91012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5226,25 +5230,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5254,10 +5258,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578059</v>
+        <v>577906</v>
       </c>
       <c r="R41" t="n">
-        <v>6340412</v>
+        <v>6340336</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5418,10 +5422,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124303500</v>
+        <v>124304453</v>
       </c>
       <c r="B43" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5430,50 +5434,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578140</v>
+        <v>578088</v>
       </c>
       <c r="R43" t="n">
-        <v>6340418</v>
+        <v>6340470</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5503,6 +5498,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5529,10 +5529,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124797728</v>
+        <v>124795887</v>
       </c>
       <c r="B44" t="n">
-        <v>57529</v>
+        <v>96390</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5541,25 +5541,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5569,13 +5569,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578047</v>
+        <v>578113</v>
       </c>
       <c r="R44" t="n">
-        <v>6340449</v>
+        <v>6340445</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5605,11 +5605,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5636,10 +5631,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124797132</v>
+        <v>124797764</v>
       </c>
       <c r="B45" t="n">
-        <v>5196</v>
+        <v>57666</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5648,41 +5643,46 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578099</v>
+        <v>578056</v>
       </c>
       <c r="R45" t="n">
-        <v>6340486</v>
+        <v>6340468</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5712,11 +5712,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5736,17 +5731,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124796306</v>
+        <v>124797132</v>
       </c>
       <c r="B46" t="n">
-        <v>79428</v>
+        <v>5196</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5755,41 +5750,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577987</v>
+        <v>578099</v>
       </c>
       <c r="R46" t="n">
-        <v>6340434</v>
+        <v>6340486</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5819,6 +5814,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5833,22 +5833,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124795874</v>
+        <v>124799230</v>
       </c>
       <c r="B47" t="n">
-        <v>79004</v>
+        <v>92210</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5857,38 +5857,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1639</v>
+        <v>2075</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578029</v>
+        <v>577970</v>
       </c>
       <c r="R47" t="n">
-        <v>6340450</v>
+        <v>6340397</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5947,10 +5947,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124799230</v>
+        <v>124796185</v>
       </c>
       <c r="B48" t="n">
-        <v>92210</v>
+        <v>79428</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5963,21 +5963,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2075</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5987,10 +5987,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577970</v>
+        <v>578013</v>
       </c>
       <c r="R48" t="n">
-        <v>6340397</v>
+        <v>6340449</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6049,10 +6049,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124795744</v>
+        <v>124795772</v>
       </c>
       <c r="B49" t="n">
-        <v>79428</v>
+        <v>96354</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6065,37 +6065,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578042</v>
+        <v>578110</v>
       </c>
       <c r="R49" t="n">
         <v>6340428</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6139,22 +6139,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124795621</v>
+        <v>124796768</v>
       </c>
       <c r="B50" t="n">
-        <v>57995</v>
+        <v>79428</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6167,46 +6167,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103018</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Boda, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578049</v>
+        <v>578118</v>
       </c>
       <c r="R50" t="n">
-        <v>6340376</v>
+        <v>6340459</v>
       </c>
       <c r="S50" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6250,22 +6241,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124797764</v>
+        <v>124796529</v>
       </c>
       <c r="B51" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6278,42 +6269,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578056</v>
+        <v>577974</v>
       </c>
       <c r="R51" t="n">
-        <v>6340468</v>
+        <v>6340427</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6357,22 +6343,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124795772</v>
+        <v>124795744</v>
       </c>
       <c r="B52" t="n">
-        <v>96354</v>
+        <v>79428</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6385,37 +6371,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578110</v>
+        <v>578042</v>
       </c>
       <c r="R52" t="n">
         <v>6340428</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6459,22 +6445,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124796768</v>
+        <v>124796606</v>
       </c>
       <c r="B53" t="n">
-        <v>79428</v>
+        <v>92239</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6483,25 +6469,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>26</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6511,13 +6497,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578118</v>
+        <v>578096</v>
       </c>
       <c r="R53" t="n">
-        <v>6340459</v>
+        <v>6340479</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6680,10 +6666,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124795668</v>
+        <v>124797728</v>
       </c>
       <c r="B55" t="n">
-        <v>91023</v>
+        <v>57529</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6692,45 +6678,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578042</v>
+        <v>578047</v>
       </c>
       <c r="R55" t="n">
-        <v>6340382</v>
+        <v>6340449</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6760,6 +6742,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6774,19 +6761,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124796060</v>
+        <v>124796306</v>
       </c>
       <c r="B56" t="n">
         <v>79428</v>
@@ -6826,10 +6813,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578034</v>
+        <v>577987</v>
       </c>
       <c r="R56" t="n">
-        <v>6340457</v>
+        <v>6340434</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6888,10 +6875,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124796245</v>
+        <v>124795621</v>
       </c>
       <c r="B57" t="n">
-        <v>79004</v>
+        <v>57995</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6900,41 +6887,50 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1639</v>
+        <v>103018</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Mosse Hjortshult, Boda, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>577987</v>
+        <v>578049</v>
       </c>
       <c r="R57" t="n">
-        <v>6340434</v>
+        <v>6340376</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6990,10 +6986,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124796529</v>
+        <v>124797831</v>
       </c>
       <c r="B58" t="n">
-        <v>79891</v>
+        <v>96354</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7006,37 +7002,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>577974</v>
+        <v>578055</v>
       </c>
       <c r="R58" t="n">
-        <v>6340427</v>
+        <v>6340450</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7080,22 +7076,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124797831</v>
+        <v>124796245</v>
       </c>
       <c r="B59" t="n">
-        <v>96354</v>
+        <v>79004</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7104,41 +7100,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>1639</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578055</v>
+        <v>577987</v>
       </c>
       <c r="R59" t="n">
-        <v>6340450</v>
+        <v>6340434</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7182,22 +7178,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124796460</v>
+        <v>124796269</v>
       </c>
       <c r="B60" t="n">
-        <v>95423</v>
+        <v>5361</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7206,25 +7202,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2671</v>
+        <v>101728</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7234,13 +7230,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578092</v>
+        <v>578107</v>
       </c>
       <c r="R60" t="n">
-        <v>6340465</v>
+        <v>6340454</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7270,6 +7266,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7296,10 +7297,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124796185</v>
+        <v>124795874</v>
       </c>
       <c r="B61" t="n">
-        <v>79428</v>
+        <v>79004</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7308,38 +7309,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>1639</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578013</v>
+        <v>578029</v>
       </c>
       <c r="R61" t="n">
-        <v>6340449</v>
+        <v>6340450</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7398,10 +7399,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124795887</v>
+        <v>124795668</v>
       </c>
       <c r="B62" t="n">
-        <v>96390</v>
+        <v>91023</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7414,37 +7415,41 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2590</v>
+        <v>1205</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578113</v>
+        <v>578042</v>
       </c>
       <c r="R62" t="n">
-        <v>6340445</v>
+        <v>6340382</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7488,22 +7493,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124796269</v>
+        <v>124796460</v>
       </c>
       <c r="B63" t="n">
-        <v>5361</v>
+        <v>95423</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7512,25 +7517,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>101728</v>
+        <v>2671</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7540,13 +7545,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578107</v>
+        <v>578092</v>
       </c>
       <c r="R63" t="n">
-        <v>6340454</v>
+        <v>6340465</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7576,11 +7581,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7607,10 +7607,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124796606</v>
+        <v>124796060</v>
       </c>
       <c r="B64" t="n">
-        <v>92239</v>
+        <v>79428</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7619,41 +7619,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>26</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578096</v>
+        <v>578034</v>
       </c>
       <c r="R64" t="n">
-        <v>6340479</v>
+        <v>6340457</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7697,12 +7697,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7815,10 +7815,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124825677</v>
+        <v>124825691</v>
       </c>
       <c r="B66" t="n">
-        <v>96390</v>
+        <v>4772</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7831,27 +7831,28 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2590</v>
+        <v>100299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7859,10 +7860,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578131</v>
+        <v>578135</v>
       </c>
       <c r="R66" t="n">
-        <v>6340387</v>
+        <v>6340398</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7895,6 +7896,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7922,10 +7928,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124825691</v>
+        <v>124825677</v>
       </c>
       <c r="B67" t="n">
-        <v>4772</v>
+        <v>96390</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7938,28 +7944,27 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100299</v>
+        <v>2590</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7967,10 +7972,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>578135</v>
+        <v>578131</v>
       </c>
       <c r="R67" t="n">
-        <v>6340398</v>
+        <v>6340387</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8003,11 +8008,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -7088,10 +7088,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124796245</v>
+        <v>124796269</v>
       </c>
       <c r="B59" t="n">
-        <v>79004</v>
+        <v>5361</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7100,41 +7100,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1639</v>
+        <v>101728</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>577987</v>
+        <v>578107</v>
       </c>
       <c r="R59" t="n">
-        <v>6340434</v>
+        <v>6340454</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7164,6 +7164,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7178,22 +7183,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124796269</v>
+        <v>124796245</v>
       </c>
       <c r="B60" t="n">
-        <v>5361</v>
+        <v>79004</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7202,41 +7207,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>101728</v>
+        <v>1639</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578107</v>
+        <v>577987</v>
       </c>
       <c r="R60" t="n">
-        <v>6340454</v>
+        <v>6340434</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7266,11 +7271,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7285,12 +7285,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4597,7 +4597,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124306142</v>
+        <v>124304628</v>
       </c>
       <c r="B35" t="n">
         <v>95705</v>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577937</v>
+        <v>578054</v>
       </c>
       <c r="R35" t="n">
-        <v>6340345</v>
+        <v>6340399</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124303500</v>
+        <v>124308072</v>
       </c>
       <c r="B36" t="n">
-        <v>56722</v>
+        <v>105117</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4715,46 +4715,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578140</v>
+        <v>578059</v>
       </c>
       <c r="R36" t="n">
-        <v>6340418</v>
+        <v>6340412</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4810,10 +4801,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124307670</v>
+        <v>124303500</v>
       </c>
       <c r="B37" t="n">
-        <v>95423</v>
+        <v>56722</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4826,37 +4817,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2671</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578089</v>
+        <v>578140</v>
       </c>
       <c r="R37" t="n">
-        <v>6340417</v>
+        <v>6340418</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4912,10 +4912,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124304628</v>
+        <v>124304453</v>
       </c>
       <c r="B38" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4924,25 +4924,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4952,13 +4952,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578054</v>
+        <v>578088</v>
       </c>
       <c r="R38" t="n">
-        <v>6340399</v>
+        <v>6340470</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4988,6 +4988,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5014,10 +5019,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124305419</v>
+        <v>124306142</v>
       </c>
       <c r="B39" t="n">
-        <v>95423</v>
+        <v>95705</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5030,21 +5035,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2671</v>
+        <v>2180</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5054,10 +5059,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577961</v>
+        <v>577937</v>
       </c>
       <c r="R39" t="n">
-        <v>6340362</v>
+        <v>6340345</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5116,10 +5121,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124308072</v>
+        <v>124307670</v>
       </c>
       <c r="B40" t="n">
-        <v>105117</v>
+        <v>95423</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5132,21 +5137,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>2671</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5156,13 +5161,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578059</v>
+        <v>578089</v>
       </c>
       <c r="R40" t="n">
-        <v>6340412</v>
+        <v>6340417</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5218,10 +5223,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124306409</v>
+        <v>124305419</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>95423</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5230,25 +5235,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>2671</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5258,10 +5263,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577906</v>
+        <v>577961</v>
       </c>
       <c r="R41" t="n">
-        <v>6340336</v>
+        <v>6340362</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5422,10 +5427,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124304453</v>
+        <v>124306409</v>
       </c>
       <c r="B43" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5438,21 +5443,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5462,10 +5467,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578088</v>
+        <v>577906</v>
       </c>
       <c r="R43" t="n">
-        <v>6340470</v>
+        <v>6340336</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5498,11 +5503,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5529,10 +5529,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124795887</v>
+        <v>124797831</v>
       </c>
       <c r="B44" t="n">
-        <v>96390</v>
+        <v>96354</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5541,25 +5541,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5569,13 +5569,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578113</v>
+        <v>578055</v>
       </c>
       <c r="R44" t="n">
-        <v>6340445</v>
+        <v>6340450</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5631,10 +5631,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124797764</v>
+        <v>124796185</v>
       </c>
       <c r="B45" t="n">
-        <v>57666</v>
+        <v>79428</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5647,42 +5647,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578056</v>
+        <v>578013</v>
       </c>
       <c r="R45" t="n">
-        <v>6340468</v>
+        <v>6340449</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5726,22 +5721,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124797132</v>
+        <v>124796606</v>
       </c>
       <c r="B46" t="n">
-        <v>5196</v>
+        <v>92239</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5754,21 +5749,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>26</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5778,10 +5773,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578099</v>
+        <v>578096</v>
       </c>
       <c r="R46" t="n">
-        <v>6340486</v>
+        <v>6340479</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5814,11 +5809,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5845,10 +5835,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124799230</v>
+        <v>124796245</v>
       </c>
       <c r="B47" t="n">
-        <v>92210</v>
+        <v>79004</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5857,25 +5847,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2075</v>
+        <v>1639</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5885,10 +5875,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577970</v>
+        <v>577987</v>
       </c>
       <c r="R47" t="n">
-        <v>6340397</v>
+        <v>6340434</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5947,10 +5937,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124796185</v>
+        <v>124795621</v>
       </c>
       <c r="B48" t="n">
-        <v>79428</v>
+        <v>57995</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5963,37 +5953,46 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>103018</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Mosse Hjortshult, Boda, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578013</v>
+        <v>578049</v>
       </c>
       <c r="R48" t="n">
-        <v>6340449</v>
+        <v>6340376</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6049,10 +6048,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124795772</v>
+        <v>124797728</v>
       </c>
       <c r="B49" t="n">
-        <v>96354</v>
+        <v>57529</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6065,21 +6064,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6089,13 +6088,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578110</v>
+        <v>578047</v>
       </c>
       <c r="R49" t="n">
-        <v>6340428</v>
+        <v>6340449</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6125,6 +6124,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6144,17 +6148,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124796768</v>
+        <v>124795887</v>
       </c>
       <c r="B50" t="n">
-        <v>79428</v>
+        <v>96390</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6163,25 +6167,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>2590</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6191,10 +6195,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578118</v>
+        <v>578113</v>
       </c>
       <c r="R50" t="n">
-        <v>6340459</v>
+        <v>6340445</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6253,10 +6257,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124796529</v>
+        <v>124796306</v>
       </c>
       <c r="B51" t="n">
-        <v>79891</v>
+        <v>79428</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6269,21 +6273,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6293,10 +6297,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577974</v>
+        <v>577987</v>
       </c>
       <c r="R51" t="n">
-        <v>6340427</v>
+        <v>6340434</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6355,10 +6359,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124795744</v>
+        <v>124797648</v>
       </c>
       <c r="B52" t="n">
-        <v>79428</v>
+        <v>8447</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6367,41 +6371,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578042</v>
+        <v>578060</v>
       </c>
       <c r="R52" t="n">
-        <v>6340428</v>
+        <v>6340459</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6431,6 +6435,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6445,22 +6454,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124796606</v>
+        <v>124796529</v>
       </c>
       <c r="B53" t="n">
-        <v>92239</v>
+        <v>79891</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6469,41 +6478,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>26</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578096</v>
+        <v>577974</v>
       </c>
       <c r="R53" t="n">
-        <v>6340479</v>
+        <v>6340427</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6547,22 +6556,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124797648</v>
+        <v>124796060</v>
       </c>
       <c r="B54" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6571,41 +6580,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578060</v>
+        <v>578034</v>
       </c>
       <c r="R54" t="n">
-        <v>6340459</v>
+        <v>6340457</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6635,11 +6644,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6654,22 +6658,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124797728</v>
+        <v>124796768</v>
       </c>
       <c r="B55" t="n">
-        <v>57529</v>
+        <v>79428</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6682,21 +6686,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6706,13 +6710,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578047</v>
+        <v>578118</v>
       </c>
       <c r="R55" t="n">
-        <v>6340449</v>
+        <v>6340459</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6742,11 +6746,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6773,10 +6772,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124796306</v>
+        <v>124797132</v>
       </c>
       <c r="B56" t="n">
-        <v>79428</v>
+        <v>5196</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6785,41 +6784,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>105930</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>577987</v>
+        <v>578099</v>
       </c>
       <c r="R56" t="n">
-        <v>6340434</v>
+        <v>6340486</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6849,6 +6848,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6863,22 +6867,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124795621</v>
+        <v>124796269</v>
       </c>
       <c r="B57" t="n">
-        <v>57995</v>
+        <v>5361</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6891,46 +6895,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103018</v>
+        <v>101728</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Boda, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578049</v>
+        <v>578107</v>
       </c>
       <c r="R57" t="n">
-        <v>6340376</v>
+        <v>6340454</v>
       </c>
       <c r="S57" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6960,6 +6955,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6974,19 +6974,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124797831</v>
+        <v>124795772</v>
       </c>
       <c r="B58" t="n">
         <v>96354</v>
@@ -7026,13 +7026,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578055</v>
+        <v>578110</v>
       </c>
       <c r="R58" t="n">
-        <v>6340450</v>
+        <v>6340428</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7081,17 +7081,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124796269</v>
+        <v>124795668</v>
       </c>
       <c r="B59" t="n">
-        <v>5361</v>
+        <v>91023</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7100,41 +7100,45 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>101728</v>
+        <v>1205</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578107</v>
+        <v>578042</v>
       </c>
       <c r="R59" t="n">
-        <v>6340454</v>
+        <v>6340382</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7164,11 +7168,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7183,22 +7182,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124796245</v>
+        <v>124799230</v>
       </c>
       <c r="B60" t="n">
-        <v>79004</v>
+        <v>92210</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7207,25 +7206,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1639</v>
+        <v>2075</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7235,10 +7234,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577987</v>
+        <v>577970</v>
       </c>
       <c r="R60" t="n">
-        <v>6340434</v>
+        <v>6340397</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7297,10 +7296,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124795874</v>
+        <v>124795744</v>
       </c>
       <c r="B61" t="n">
-        <v>79004</v>
+        <v>79428</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7309,25 +7308,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1639</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7337,10 +7336,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578029</v>
+        <v>578042</v>
       </c>
       <c r="R61" t="n">
-        <v>6340450</v>
+        <v>6340428</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7399,10 +7398,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124795668</v>
+        <v>124797764</v>
       </c>
       <c r="B62" t="n">
-        <v>91023</v>
+        <v>57666</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7411,45 +7410,46 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1205</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578042</v>
+        <v>578056</v>
       </c>
       <c r="R62" t="n">
-        <v>6340382</v>
+        <v>6340468</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7493,12 +7493,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7607,10 +7607,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124796060</v>
+        <v>124795874</v>
       </c>
       <c r="B64" t="n">
-        <v>79428</v>
+        <v>79004</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7619,38 +7619,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>1639</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578034</v>
+        <v>578029</v>
       </c>
       <c r="R64" t="n">
-        <v>6340457</v>
+        <v>6340450</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7709,10 +7709,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124825657</v>
+        <v>124825677</v>
       </c>
       <c r="B65" t="n">
-        <v>92210</v>
+        <v>96390</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7721,30 +7721,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2075</v>
+        <v>2590</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7752,10 +7753,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>577974</v>
+        <v>578131</v>
       </c>
       <c r="R65" t="n">
-        <v>6340399</v>
+        <v>6340387</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7815,10 +7816,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124825691</v>
+        <v>124825657</v>
       </c>
       <c r="B66" t="n">
-        <v>4772</v>
+        <v>92210</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7827,32 +7828,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100299</v>
+        <v>2075</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7860,10 +7859,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578135</v>
+        <v>577974</v>
       </c>
       <c r="R66" t="n">
-        <v>6340398</v>
+        <v>6340399</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7896,11 +7895,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7928,10 +7922,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124825677</v>
+        <v>124825691</v>
       </c>
       <c r="B67" t="n">
-        <v>96390</v>
+        <v>4772</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7944,27 +7938,28 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2590</v>
+        <v>100299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7972,10 +7967,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>578131</v>
+        <v>578135</v>
       </c>
       <c r="R67" t="n">
-        <v>6340387</v>
+        <v>6340398</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8008,6 +8003,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4597,7 +4597,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124304628</v>
+        <v>124306142</v>
       </c>
       <c r="B35" t="n">
         <v>95705</v>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578054</v>
+        <v>577937</v>
       </c>
       <c r="R35" t="n">
-        <v>6340399</v>
+        <v>6340345</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124308072</v>
+        <v>124306409</v>
       </c>
       <c r="B36" t="n">
-        <v>105117</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4711,25 +4711,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4739,10 +4739,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578059</v>
+        <v>577906</v>
       </c>
       <c r="R36" t="n">
-        <v>6340412</v>
+        <v>6340336</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4801,10 +4801,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124303500</v>
+        <v>124304453</v>
       </c>
       <c r="B37" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4813,50 +4813,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578140</v>
+        <v>578088</v>
       </c>
       <c r="R37" t="n">
-        <v>6340418</v>
+        <v>6340470</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4886,6 +4877,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4912,10 +4908,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124304453</v>
+        <v>124307670</v>
       </c>
       <c r="B38" t="n">
-        <v>57529</v>
+        <v>95423</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4924,25 +4920,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>2671</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4952,13 +4948,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578088</v>
+        <v>578089</v>
       </c>
       <c r="R38" t="n">
-        <v>6340470</v>
+        <v>6340417</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4988,11 +4984,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5019,10 +5010,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124306142</v>
+        <v>124303584</v>
       </c>
       <c r="B39" t="n">
-        <v>95705</v>
+        <v>91032</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5031,25 +5022,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5059,10 +5050,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577937</v>
+        <v>578146</v>
       </c>
       <c r="R39" t="n">
-        <v>6340345</v>
+        <v>6340431</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5121,10 +5112,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124307670</v>
+        <v>124304628</v>
       </c>
       <c r="B40" t="n">
-        <v>95423</v>
+        <v>95705</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5137,21 +5128,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2671</v>
+        <v>2180</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5161,13 +5152,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578089</v>
+        <v>578054</v>
       </c>
       <c r="R40" t="n">
-        <v>6340417</v>
+        <v>6340399</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5223,10 +5214,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124305419</v>
+        <v>124303500</v>
       </c>
       <c r="B41" t="n">
-        <v>95423</v>
+        <v>56722</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5239,37 +5230,46 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2671</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577961</v>
+        <v>578140</v>
       </c>
       <c r="R41" t="n">
-        <v>6340362</v>
+        <v>6340418</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5325,10 +5325,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124303584</v>
+        <v>124305419</v>
       </c>
       <c r="B42" t="n">
-        <v>91032</v>
+        <v>95423</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5337,25 +5337,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578146</v>
+        <v>577961</v>
       </c>
       <c r="R42" t="n">
-        <v>6340431</v>
+        <v>6340362</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5427,10 +5427,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124306409</v>
+        <v>124308072</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>105117</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5439,25 +5439,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577906</v>
+        <v>578059</v>
       </c>
       <c r="R43" t="n">
-        <v>6340336</v>
+        <v>6340412</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5529,10 +5529,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124797831</v>
+        <v>124799230</v>
       </c>
       <c r="B44" t="n">
-        <v>96354</v>
+        <v>92210</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5545,37 +5545,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>2075</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578055</v>
+        <v>577970</v>
       </c>
       <c r="R44" t="n">
-        <v>6340450</v>
+        <v>6340397</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5619,22 +5619,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124796185</v>
+        <v>124795772</v>
       </c>
       <c r="B45" t="n">
-        <v>79428</v>
+        <v>96354</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5647,37 +5647,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578013</v>
+        <v>578110</v>
       </c>
       <c r="R45" t="n">
-        <v>6340449</v>
+        <v>6340428</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5721,22 +5721,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124796606</v>
+        <v>124797728</v>
       </c>
       <c r="B46" t="n">
-        <v>92239</v>
+        <v>57529</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5745,25 +5745,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>26</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5773,10 +5773,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578096</v>
+        <v>578047</v>
       </c>
       <c r="R46" t="n">
-        <v>6340479</v>
+        <v>6340449</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5809,6 +5809,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5835,10 +5840,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124796245</v>
+        <v>124796768</v>
       </c>
       <c r="B47" t="n">
-        <v>79004</v>
+        <v>79428</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5847,41 +5852,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1639</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577987</v>
+        <v>578118</v>
       </c>
       <c r="R47" t="n">
-        <v>6340434</v>
+        <v>6340459</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5925,22 +5930,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124795621</v>
+        <v>124797831</v>
       </c>
       <c r="B48" t="n">
-        <v>57995</v>
+        <v>96354</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5953,46 +5958,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103018</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Boda, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578049</v>
+        <v>578055</v>
       </c>
       <c r="R48" t="n">
-        <v>6340376</v>
+        <v>6340450</v>
       </c>
       <c r="S48" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6036,22 +6032,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124797728</v>
+        <v>124795874</v>
       </c>
       <c r="B49" t="n">
-        <v>57529</v>
+        <v>79004</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6060,41 +6056,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>1639</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578047</v>
+        <v>578029</v>
       </c>
       <c r="R49" t="n">
-        <v>6340449</v>
+        <v>6340450</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6124,11 +6120,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6143,22 +6134,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124795887</v>
+        <v>124797132</v>
       </c>
       <c r="B50" t="n">
-        <v>96390</v>
+        <v>5196</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6171,21 +6162,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2590</v>
+        <v>105930</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6195,13 +6186,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578113</v>
+        <v>578099</v>
       </c>
       <c r="R50" t="n">
-        <v>6340445</v>
+        <v>6340486</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6231,6 +6222,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6257,10 +6253,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124796306</v>
+        <v>124796269</v>
       </c>
       <c r="B51" t="n">
-        <v>79428</v>
+        <v>5361</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6273,37 +6269,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>101728</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577987</v>
+        <v>578107</v>
       </c>
       <c r="R51" t="n">
-        <v>6340434</v>
+        <v>6340454</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6333,6 +6329,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6347,12 +6348,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6466,10 +6467,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124796529</v>
+        <v>124797764</v>
       </c>
       <c r="B53" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6482,37 +6483,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577974</v>
+        <v>578056</v>
       </c>
       <c r="R53" t="n">
-        <v>6340427</v>
+        <v>6340468</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6556,22 +6562,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124796060</v>
+        <v>124796606</v>
       </c>
       <c r="B54" t="n">
-        <v>79428</v>
+        <v>92239</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6580,41 +6586,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>26</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578034</v>
+        <v>578096</v>
       </c>
       <c r="R54" t="n">
-        <v>6340457</v>
+        <v>6340479</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6658,22 +6664,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124796768</v>
+        <v>124795887</v>
       </c>
       <c r="B55" t="n">
-        <v>79428</v>
+        <v>96390</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6682,25 +6688,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>2590</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6710,10 +6716,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578118</v>
+        <v>578113</v>
       </c>
       <c r="R55" t="n">
-        <v>6340459</v>
+        <v>6340445</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6772,10 +6778,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124797132</v>
+        <v>124795668</v>
       </c>
       <c r="B56" t="n">
-        <v>5196</v>
+        <v>91023</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6788,37 +6794,41 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>105930</v>
+        <v>1205</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578099</v>
+        <v>578042</v>
       </c>
       <c r="R56" t="n">
-        <v>6340486</v>
+        <v>6340382</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6848,11 +6858,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6867,22 +6872,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124796269</v>
+        <v>124796245</v>
       </c>
       <c r="B57" t="n">
-        <v>5361</v>
+        <v>79004</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6891,41 +6896,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>101728</v>
+        <v>1639</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578107</v>
+        <v>577987</v>
       </c>
       <c r="R57" t="n">
-        <v>6340454</v>
+        <v>6340434</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6955,11 +6960,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6974,22 +6974,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124795772</v>
+        <v>124796185</v>
       </c>
       <c r="B58" t="n">
-        <v>96354</v>
+        <v>79428</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7002,37 +7002,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578110</v>
+        <v>578013</v>
       </c>
       <c r="R58" t="n">
-        <v>6340428</v>
+        <v>6340449</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7076,22 +7076,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124795668</v>
+        <v>124795621</v>
       </c>
       <c r="B59" t="n">
-        <v>91023</v>
+        <v>57995</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7100,45 +7100,50 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1205</v>
+        <v>103018</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
+          <t>Mosse Hjortshult, Boda, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578042</v>
+        <v>578049</v>
       </c>
       <c r="R59" t="n">
-        <v>6340382</v>
+        <v>6340376</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7194,10 +7199,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124799230</v>
+        <v>124796460</v>
       </c>
       <c r="B60" t="n">
-        <v>92210</v>
+        <v>95423</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7206,41 +7211,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2075</v>
+        <v>2671</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577970</v>
+        <v>578092</v>
       </c>
       <c r="R60" t="n">
-        <v>6340397</v>
+        <v>6340465</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7284,22 +7289,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124795744</v>
+        <v>124796529</v>
       </c>
       <c r="B61" t="n">
-        <v>79428</v>
+        <v>79891</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7312,34 +7317,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578042</v>
+        <v>577974</v>
       </c>
       <c r="R61" t="n">
-        <v>6340428</v>
+        <v>6340427</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7398,10 +7403,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124797764</v>
+        <v>124796306</v>
       </c>
       <c r="B62" t="n">
-        <v>57666</v>
+        <v>79428</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7414,42 +7419,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578056</v>
+        <v>577987</v>
       </c>
       <c r="R62" t="n">
-        <v>6340468</v>
+        <v>6340434</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7493,22 +7493,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124796460</v>
+        <v>124795744</v>
       </c>
       <c r="B63" t="n">
-        <v>95423</v>
+        <v>79428</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7517,41 +7517,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2671</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578092</v>
+        <v>578042</v>
       </c>
       <c r="R63" t="n">
-        <v>6340465</v>
+        <v>6340428</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7595,22 +7595,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124795874</v>
+        <v>124796060</v>
       </c>
       <c r="B64" t="n">
-        <v>79004</v>
+        <v>79428</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7619,38 +7619,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1639</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578029</v>
+        <v>578034</v>
       </c>
       <c r="R64" t="n">
-        <v>6340450</v>
+        <v>6340457</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -5733,10 +5733,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124797728</v>
+        <v>124796768</v>
       </c>
       <c r="B46" t="n">
-        <v>57529</v>
+        <v>79428</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5749,21 +5749,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5773,13 +5773,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578047</v>
+        <v>578118</v>
       </c>
       <c r="R46" t="n">
-        <v>6340449</v>
+        <v>6340459</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5809,11 +5809,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5840,10 +5835,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124796768</v>
+        <v>124797728</v>
       </c>
       <c r="B47" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5856,21 +5851,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5880,13 +5875,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578118</v>
+        <v>578047</v>
       </c>
       <c r="R47" t="n">
-        <v>6340459</v>
+        <v>6340449</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5916,6 +5911,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6146,10 +6146,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124797132</v>
+        <v>124796269</v>
       </c>
       <c r="B50" t="n">
-        <v>5196</v>
+        <v>5361</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6158,25 +6158,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>105930</v>
+        <v>101728</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578099</v>
+        <v>578107</v>
       </c>
       <c r="R50" t="n">
-        <v>6340486</v>
+        <v>6340454</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6253,10 +6253,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124796269</v>
+        <v>124797132</v>
       </c>
       <c r="B51" t="n">
-        <v>5361</v>
+        <v>5196</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6265,25 +6265,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>101728</v>
+        <v>105930</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6293,10 +6293,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578107</v>
+        <v>578099</v>
       </c>
       <c r="R51" t="n">
-        <v>6340454</v>
+        <v>6340486</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Kläckhål</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4597,10 +4597,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124306142</v>
+        <v>124305419</v>
       </c>
       <c r="B35" t="n">
-        <v>95705</v>
+        <v>95423</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>2671</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577937</v>
+        <v>577961</v>
       </c>
       <c r="R35" t="n">
-        <v>6340345</v>
+        <v>6340362</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124306409</v>
+        <v>124303584</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>91032</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4715,21 +4715,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4739,10 +4739,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577906</v>
+        <v>578146</v>
       </c>
       <c r="R36" t="n">
-        <v>6340336</v>
+        <v>6340431</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4801,10 +4801,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124304453</v>
+        <v>124307670</v>
       </c>
       <c r="B37" t="n">
-        <v>57529</v>
+        <v>95423</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4813,25 +4813,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>2671</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4841,13 +4841,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578088</v>
+        <v>578089</v>
       </c>
       <c r="R37" t="n">
-        <v>6340470</v>
+        <v>6340417</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4877,11 +4877,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4908,10 +4903,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124307670</v>
+        <v>124303500</v>
       </c>
       <c r="B38" t="n">
-        <v>95423</v>
+        <v>56722</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4924,37 +4919,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2671</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578089</v>
+        <v>578140</v>
       </c>
       <c r="R38" t="n">
-        <v>6340417</v>
+        <v>6340418</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5010,10 +5014,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124303584</v>
+        <v>124306409</v>
       </c>
       <c r="B39" t="n">
-        <v>91032</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5026,21 +5030,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5050,10 +5054,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578146</v>
+        <v>577906</v>
       </c>
       <c r="R39" t="n">
-        <v>6340431</v>
+        <v>6340336</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5112,7 +5116,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124304628</v>
+        <v>124306142</v>
       </c>
       <c r="B40" t="n">
         <v>95705</v>
@@ -5152,13 +5156,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578054</v>
+        <v>577937</v>
       </c>
       <c r="R40" t="n">
-        <v>6340399</v>
+        <v>6340345</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5214,10 +5218,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124303500</v>
+        <v>124304628</v>
       </c>
       <c r="B41" t="n">
-        <v>56722</v>
+        <v>95705</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5230,46 +5234,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578140</v>
+        <v>578054</v>
       </c>
       <c r="R41" t="n">
-        <v>6340418</v>
+        <v>6340399</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5325,10 +5320,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124305419</v>
+        <v>124304453</v>
       </c>
       <c r="B42" t="n">
-        <v>95423</v>
+        <v>57529</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5337,25 +5332,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2671</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5365,10 +5360,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577961</v>
+        <v>578088</v>
       </c>
       <c r="R42" t="n">
-        <v>6340362</v>
+        <v>6340470</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5401,6 +5396,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5529,10 +5529,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124799230</v>
+        <v>124796306</v>
       </c>
       <c r="B44" t="n">
-        <v>92210</v>
+        <v>79428</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2075</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577970</v>
+        <v>577987</v>
       </c>
       <c r="R44" t="n">
-        <v>6340397</v>
+        <v>6340434</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5631,10 +5631,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124795772</v>
+        <v>124795874</v>
       </c>
       <c r="B45" t="n">
-        <v>96354</v>
+        <v>79004</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5643,41 +5643,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>1639</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578110</v>
+        <v>578029</v>
       </c>
       <c r="R45" t="n">
-        <v>6340428</v>
+        <v>6340450</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5721,19 +5721,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124796768</v>
+        <v>124796060</v>
       </c>
       <c r="B46" t="n">
         <v>79428</v>
@@ -5769,17 +5769,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578118</v>
+        <v>578034</v>
       </c>
       <c r="R46" t="n">
-        <v>6340459</v>
+        <v>6340457</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5823,12 +5823,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5942,10 +5942,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124797831</v>
+        <v>124796768</v>
       </c>
       <c r="B48" t="n">
-        <v>96354</v>
+        <v>79428</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5958,21 +5958,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5982,13 +5982,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578055</v>
+        <v>578118</v>
       </c>
       <c r="R48" t="n">
-        <v>6340450</v>
+        <v>6340459</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6044,10 +6044,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124795874</v>
+        <v>124796269</v>
       </c>
       <c r="B49" t="n">
-        <v>79004</v>
+        <v>5361</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6056,41 +6056,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1639</v>
+        <v>101728</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578029</v>
+        <v>578107</v>
       </c>
       <c r="R49" t="n">
-        <v>6340450</v>
+        <v>6340454</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6120,6 +6120,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6134,22 +6139,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124796269</v>
+        <v>124797764</v>
       </c>
       <c r="B50" t="n">
-        <v>5361</v>
+        <v>57666</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6162,37 +6167,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>101728</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578107</v>
+        <v>578056</v>
       </c>
       <c r="R50" t="n">
-        <v>6340454</v>
+        <v>6340468</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6222,11 +6232,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6246,17 +6251,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124797132</v>
+        <v>124795621</v>
       </c>
       <c r="B51" t="n">
-        <v>5196</v>
+        <v>57995</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6265,41 +6270,50 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>105930</v>
+        <v>103018</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Mosse Hjortshult, Boda, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578099</v>
+        <v>578049</v>
       </c>
       <c r="R51" t="n">
-        <v>6340486</v>
+        <v>6340376</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6329,11 +6343,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6348,22 +6357,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124797648</v>
+        <v>124795668</v>
       </c>
       <c r="B52" t="n">
-        <v>8447</v>
+        <v>91023</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6376,37 +6385,41 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>1205</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578060</v>
+        <v>578042</v>
       </c>
       <c r="R52" t="n">
-        <v>6340459</v>
+        <v>6340382</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6436,11 +6449,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6455,22 +6463,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124797764</v>
+        <v>124797648</v>
       </c>
       <c r="B53" t="n">
-        <v>57666</v>
+        <v>8447</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6479,46 +6487,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578056</v>
+        <v>578060</v>
       </c>
       <c r="R53" t="n">
-        <v>6340468</v>
+        <v>6340459</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6548,6 +6551,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6574,10 +6582,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124796606</v>
+        <v>124795887</v>
       </c>
       <c r="B54" t="n">
-        <v>92239</v>
+        <v>96390</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6590,21 +6598,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>26</v>
+        <v>2590</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6614,13 +6622,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578096</v>
+        <v>578113</v>
       </c>
       <c r="R54" t="n">
-        <v>6340479</v>
+        <v>6340445</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6676,10 +6684,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124795887</v>
+        <v>124796460</v>
       </c>
       <c r="B55" t="n">
-        <v>96390</v>
+        <v>95423</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6692,21 +6700,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2590</v>
+        <v>2671</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6716,10 +6724,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578113</v>
+        <v>578092</v>
       </c>
       <c r="R55" t="n">
-        <v>6340445</v>
+        <v>6340465</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6778,10 +6786,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124795668</v>
+        <v>124795744</v>
       </c>
       <c r="B56" t="n">
-        <v>91023</v>
+        <v>79428</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6790,42 +6798,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1205</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
         <v>578042</v>
       </c>
       <c r="R56" t="n">
-        <v>6340382</v>
+        <v>6340428</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6884,10 +6888,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124796245</v>
+        <v>124797132</v>
       </c>
       <c r="B57" t="n">
-        <v>79004</v>
+        <v>5196</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6900,37 +6904,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1639</v>
+        <v>105930</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>577987</v>
+        <v>578099</v>
       </c>
       <c r="R57" t="n">
-        <v>6340434</v>
+        <v>6340486</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6960,6 +6964,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6974,22 +6983,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124796185</v>
+        <v>124795772</v>
       </c>
       <c r="B58" t="n">
-        <v>79428</v>
+        <v>96354</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7002,37 +7011,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578013</v>
+        <v>578110</v>
       </c>
       <c r="R58" t="n">
-        <v>6340449</v>
+        <v>6340428</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7076,22 +7085,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124795621</v>
+        <v>124796185</v>
       </c>
       <c r="B59" t="n">
-        <v>57995</v>
+        <v>79428</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7104,46 +7113,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103018</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Boda, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578049</v>
+        <v>578013</v>
       </c>
       <c r="R59" t="n">
-        <v>6340376</v>
+        <v>6340449</v>
       </c>
       <c r="S59" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7199,10 +7199,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124796460</v>
+        <v>124796245</v>
       </c>
       <c r="B60" t="n">
-        <v>95423</v>
+        <v>79004</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7215,37 +7215,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2671</v>
+        <v>1639</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578092</v>
+        <v>577987</v>
       </c>
       <c r="R60" t="n">
-        <v>6340465</v>
+        <v>6340434</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7289,22 +7289,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124796529</v>
+        <v>124799230</v>
       </c>
       <c r="B61" t="n">
-        <v>79891</v>
+        <v>92210</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7317,21 +7317,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>2075</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7341,10 +7341,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>577974</v>
+        <v>577970</v>
       </c>
       <c r="R61" t="n">
-        <v>6340427</v>
+        <v>6340397</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7403,10 +7403,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124796306</v>
+        <v>124796529</v>
       </c>
       <c r="B62" t="n">
-        <v>79428</v>
+        <v>79891</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7419,21 +7419,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7443,10 +7443,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577987</v>
+        <v>577974</v>
       </c>
       <c r="R62" t="n">
-        <v>6340434</v>
+        <v>6340427</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7505,10 +7505,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124795744</v>
+        <v>124796606</v>
       </c>
       <c r="B63" t="n">
-        <v>79428</v>
+        <v>92239</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7517,41 +7517,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>26</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578042</v>
+        <v>578096</v>
       </c>
       <c r="R63" t="n">
-        <v>6340428</v>
+        <v>6340479</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7595,22 +7595,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124796060</v>
+        <v>124797831</v>
       </c>
       <c r="B64" t="n">
-        <v>79428</v>
+        <v>96354</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7623,37 +7623,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578034</v>
+        <v>578055</v>
       </c>
       <c r="R64" t="n">
-        <v>6340457</v>
+        <v>6340450</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7697,12 +7697,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -7097,10 +7097,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124796185</v>
+        <v>124796245</v>
       </c>
       <c r="B59" t="n">
-        <v>79428</v>
+        <v>79004</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7109,25 +7109,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>1639</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578013</v>
+        <v>577987</v>
       </c>
       <c r="R59" t="n">
-        <v>6340449</v>
+        <v>6340434</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7199,10 +7199,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124796245</v>
+        <v>124796185</v>
       </c>
       <c r="B60" t="n">
-        <v>79004</v>
+        <v>79428</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7211,25 +7211,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1639</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577987</v>
+        <v>578013</v>
       </c>
       <c r="R60" t="n">
-        <v>6340434</v>
+        <v>6340449</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7403,10 +7403,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124796529</v>
+        <v>124796606</v>
       </c>
       <c r="B62" t="n">
-        <v>79891</v>
+        <v>92239</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7415,41 +7415,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>26</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577974</v>
+        <v>578096</v>
       </c>
       <c r="R62" t="n">
-        <v>6340427</v>
+        <v>6340479</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7493,22 +7493,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124796606</v>
+        <v>124796529</v>
       </c>
       <c r="B63" t="n">
-        <v>92239</v>
+        <v>79891</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7517,41 +7517,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>26</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578096</v>
+        <v>577974</v>
       </c>
       <c r="R63" t="n">
-        <v>6340479</v>
+        <v>6340427</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7595,12 +7595,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4597,10 +4597,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124305419</v>
+        <v>124306142</v>
       </c>
       <c r="B35" t="n">
-        <v>95423</v>
+        <v>95705</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2671</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577961</v>
+        <v>577937</v>
       </c>
       <c r="R35" t="n">
-        <v>6340362</v>
+        <v>6340345</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124303584</v>
+        <v>124306409</v>
       </c>
       <c r="B36" t="n">
-        <v>91032</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4715,21 +4715,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4739,10 +4739,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578146</v>
+        <v>577906</v>
       </c>
       <c r="R36" t="n">
-        <v>6340431</v>
+        <v>6340336</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4801,10 +4801,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124307670</v>
+        <v>124303584</v>
       </c>
       <c r="B37" t="n">
-        <v>95423</v>
+        <v>91032</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4813,25 +4813,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4841,13 +4841,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578089</v>
+        <v>578146</v>
       </c>
       <c r="R37" t="n">
-        <v>6340417</v>
+        <v>6340431</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4903,10 +4903,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124303500</v>
+        <v>124308072</v>
       </c>
       <c r="B38" t="n">
-        <v>56722</v>
+        <v>105117</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4919,46 +4919,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578140</v>
+        <v>578059</v>
       </c>
       <c r="R38" t="n">
-        <v>6340418</v>
+        <v>6340412</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5014,10 +5005,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124306409</v>
+        <v>124307670</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>95423</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5026,25 +5017,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>2671</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5054,13 +5045,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577906</v>
+        <v>578089</v>
       </c>
       <c r="R39" t="n">
-        <v>6340336</v>
+        <v>6340417</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5116,7 +5107,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124306142</v>
+        <v>124304628</v>
       </c>
       <c r="B40" t="n">
         <v>95705</v>
@@ -5156,13 +5147,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577937</v>
+        <v>578054</v>
       </c>
       <c r="R40" t="n">
-        <v>6340345</v>
+        <v>6340399</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5218,10 +5209,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124304628</v>
+        <v>124303500</v>
       </c>
       <c r="B41" t="n">
-        <v>95705</v>
+        <v>56722</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5234,37 +5225,46 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578054</v>
+        <v>578140</v>
       </c>
       <c r="R41" t="n">
-        <v>6340399</v>
+        <v>6340418</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5427,10 +5427,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124308072</v>
+        <v>124305419</v>
       </c>
       <c r="B43" t="n">
-        <v>105117</v>
+        <v>95423</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5443,21 +5443,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>2671</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578059</v>
+        <v>577961</v>
       </c>
       <c r="R43" t="n">
-        <v>6340412</v>
+        <v>6340362</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5529,7 +5529,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124796306</v>
+        <v>124796768</v>
       </c>
       <c r="B44" t="n">
         <v>79428</v>
@@ -5565,17 +5565,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577987</v>
+        <v>578118</v>
       </c>
       <c r="R44" t="n">
-        <v>6340434</v>
+        <v>6340459</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5619,22 +5619,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124795874</v>
+        <v>124797831</v>
       </c>
       <c r="B45" t="n">
-        <v>79004</v>
+        <v>96354</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5643,41 +5643,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1639</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578029</v>
+        <v>578055</v>
       </c>
       <c r="R45" t="n">
         <v>6340450</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5721,19 +5721,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124796060</v>
+        <v>124796185</v>
       </c>
       <c r="B46" t="n">
         <v>79428</v>
@@ -5773,10 +5773,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578034</v>
+        <v>578013</v>
       </c>
       <c r="R46" t="n">
-        <v>6340457</v>
+        <v>6340449</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5835,10 +5835,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124797728</v>
+        <v>124796245</v>
       </c>
       <c r="B47" t="n">
-        <v>57529</v>
+        <v>79004</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5847,41 +5847,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>1639</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578047</v>
+        <v>577987</v>
       </c>
       <c r="R47" t="n">
-        <v>6340449</v>
+        <v>6340434</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5911,11 +5911,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5930,22 +5925,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124796768</v>
+        <v>124795874</v>
       </c>
       <c r="B48" t="n">
-        <v>79428</v>
+        <v>79004</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5954,41 +5949,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>1639</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578118</v>
+        <v>578029</v>
       </c>
       <c r="R48" t="n">
-        <v>6340459</v>
+        <v>6340450</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6032,22 +6027,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124796269</v>
+        <v>124797728</v>
       </c>
       <c r="B49" t="n">
-        <v>5361</v>
+        <v>57529</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6060,21 +6055,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6084,10 +6079,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578107</v>
+        <v>578047</v>
       </c>
       <c r="R49" t="n">
-        <v>6340454</v>
+        <v>6340449</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6124,7 +6119,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Kläckhål</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6151,10 +6146,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124797764</v>
+        <v>124795621</v>
       </c>
       <c r="B50" t="n">
-        <v>57666</v>
+        <v>57995</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6167,24 +6162,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -6192,17 +6191,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Mosse Hjortshult, Boda, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578056</v>
+        <v>578049</v>
       </c>
       <c r="R50" t="n">
-        <v>6340468</v>
+        <v>6340376</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6246,22 +6245,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124795621</v>
+        <v>124797132</v>
       </c>
       <c r="B51" t="n">
-        <v>57995</v>
+        <v>5196</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6270,50 +6269,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103018</v>
+        <v>105930</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Boda, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578049</v>
+        <v>578099</v>
       </c>
       <c r="R51" t="n">
-        <v>6340376</v>
+        <v>6340486</v>
       </c>
       <c r="S51" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6343,6 +6333,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6357,22 +6352,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124795668</v>
+        <v>124799230</v>
       </c>
       <c r="B52" t="n">
-        <v>91023</v>
+        <v>92210</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6381,42 +6376,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1205</v>
+        <v>2075</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Boidin</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578042</v>
+        <v>577970</v>
       </c>
       <c r="R52" t="n">
-        <v>6340382</v>
+        <v>6340397</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6475,10 +6466,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124797648</v>
+        <v>124795744</v>
       </c>
       <c r="B53" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6487,41 +6478,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578060</v>
+        <v>578042</v>
       </c>
       <c r="R53" t="n">
-        <v>6340459</v>
+        <v>6340428</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6551,11 +6542,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6570,22 +6556,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124795887</v>
+        <v>124797648</v>
       </c>
       <c r="B54" t="n">
-        <v>96390</v>
+        <v>8447</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6598,21 +6584,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6622,13 +6608,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578113</v>
+        <v>578060</v>
       </c>
       <c r="R54" t="n">
-        <v>6340445</v>
+        <v>6340459</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6658,6 +6644,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6677,17 +6668,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124796460</v>
+        <v>124795887</v>
       </c>
       <c r="B55" t="n">
-        <v>95423</v>
+        <v>96390</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6700,21 +6691,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2671</v>
+        <v>2590</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6724,10 +6715,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578092</v>
+        <v>578113</v>
       </c>
       <c r="R55" t="n">
-        <v>6340465</v>
+        <v>6340445</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6786,10 +6777,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124795744</v>
+        <v>124797764</v>
       </c>
       <c r="B56" t="n">
-        <v>79428</v>
+        <v>57666</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6802,37 +6793,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578042</v>
+        <v>578056</v>
       </c>
       <c r="R56" t="n">
-        <v>6340428</v>
+        <v>6340468</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6876,22 +6872,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124797132</v>
+        <v>124795668</v>
       </c>
       <c r="B57" t="n">
-        <v>5196</v>
+        <v>91023</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6904,37 +6900,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>105930</v>
+        <v>1205</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578099</v>
+        <v>578042</v>
       </c>
       <c r="R57" t="n">
-        <v>6340486</v>
+        <v>6340382</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6964,11 +6964,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6983,12 +6978,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7097,10 +7092,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124796245</v>
+        <v>124796060</v>
       </c>
       <c r="B59" t="n">
-        <v>79004</v>
+        <v>79428</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7109,25 +7104,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1639</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7137,10 +7132,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>577987</v>
+        <v>578034</v>
       </c>
       <c r="R59" t="n">
-        <v>6340434</v>
+        <v>6340457</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7199,7 +7194,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124796185</v>
+        <v>124796306</v>
       </c>
       <c r="B60" t="n">
         <v>79428</v>
@@ -7239,10 +7234,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578013</v>
+        <v>577987</v>
       </c>
       <c r="R60" t="n">
-        <v>6340449</v>
+        <v>6340434</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7301,10 +7296,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124799230</v>
+        <v>124796606</v>
       </c>
       <c r="B61" t="n">
-        <v>92210</v>
+        <v>92239</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7313,41 +7308,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2075</v>
+        <v>26</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>577970</v>
+        <v>578096</v>
       </c>
       <c r="R61" t="n">
-        <v>6340397</v>
+        <v>6340479</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7391,22 +7386,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124796606</v>
+        <v>124796460</v>
       </c>
       <c r="B62" t="n">
-        <v>92239</v>
+        <v>95423</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7419,21 +7414,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>26</v>
+        <v>2671</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7443,13 +7438,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578096</v>
+        <v>578092</v>
       </c>
       <c r="R62" t="n">
-        <v>6340479</v>
+        <v>6340465</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7607,10 +7602,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124797831</v>
+        <v>124796269</v>
       </c>
       <c r="B64" t="n">
-        <v>96354</v>
+        <v>5361</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7623,21 +7618,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>53</v>
+        <v>101728</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7647,10 +7642,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578055</v>
+        <v>578107</v>
       </c>
       <c r="R64" t="n">
-        <v>6340450</v>
+        <v>6340454</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7683,6 +7678,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7816,10 +7816,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124825657</v>
+        <v>124825691</v>
       </c>
       <c r="B66" t="n">
-        <v>92210</v>
+        <v>4772</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7828,30 +7828,32 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2075</v>
+        <v>100299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7859,10 +7861,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>577974</v>
+        <v>578135</v>
       </c>
       <c r="R66" t="n">
-        <v>6340399</v>
+        <v>6340398</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7895,6 +7897,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7922,10 +7929,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124825691</v>
+        <v>124825657</v>
       </c>
       <c r="B67" t="n">
-        <v>4772</v>
+        <v>92210</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7934,32 +7941,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100299</v>
+        <v>2075</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7967,10 +7972,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>578135</v>
+        <v>577974</v>
       </c>
       <c r="R67" t="n">
-        <v>6340398</v>
+        <v>6340399</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8003,11 +8008,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4597,10 +4597,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124306142</v>
+        <v>124303500</v>
       </c>
       <c r="B35" t="n">
-        <v>95705</v>
+        <v>56722</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4613,37 +4613,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577937</v>
+        <v>578140</v>
       </c>
       <c r="R35" t="n">
-        <v>6340345</v>
+        <v>6340418</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4699,10 +4708,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124306409</v>
+        <v>124304628</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>95705</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4711,25 +4720,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4739,13 +4748,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577906</v>
+        <v>578054</v>
       </c>
       <c r="R36" t="n">
-        <v>6340336</v>
+        <v>6340399</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4801,10 +4810,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124303584</v>
+        <v>124306409</v>
       </c>
       <c r="B37" t="n">
-        <v>91032</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4817,21 +4826,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4841,10 +4850,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578146</v>
+        <v>577906</v>
       </c>
       <c r="R37" t="n">
-        <v>6340431</v>
+        <v>6340336</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4903,10 +4912,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124308072</v>
+        <v>124307670</v>
       </c>
       <c r="B38" t="n">
-        <v>105117</v>
+        <v>95423</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4919,21 +4928,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>2671</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4943,13 +4952,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578059</v>
+        <v>578089</v>
       </c>
       <c r="R38" t="n">
-        <v>6340412</v>
+        <v>6340417</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5005,10 +5014,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124307670</v>
+        <v>124304453</v>
       </c>
       <c r="B39" t="n">
-        <v>95423</v>
+        <v>57529</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5017,25 +5026,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2671</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5045,13 +5054,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578089</v>
+        <v>578088</v>
       </c>
       <c r="R39" t="n">
-        <v>6340417</v>
+        <v>6340470</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5081,6 +5090,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5107,10 +5121,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124304628</v>
+        <v>124308072</v>
       </c>
       <c r="B40" t="n">
-        <v>95705</v>
+        <v>105117</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5123,21 +5137,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5147,13 +5161,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578054</v>
+        <v>578059</v>
       </c>
       <c r="R40" t="n">
-        <v>6340399</v>
+        <v>6340412</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5209,10 +5223,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124303500</v>
+        <v>124305419</v>
       </c>
       <c r="B41" t="n">
-        <v>56722</v>
+        <v>95423</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5225,46 +5239,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>2671</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578140</v>
+        <v>577961</v>
       </c>
       <c r="R41" t="n">
-        <v>6340418</v>
+        <v>6340362</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5320,10 +5325,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124304453</v>
+        <v>124303584</v>
       </c>
       <c r="B42" t="n">
-        <v>57529</v>
+        <v>91032</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5336,21 +5341,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5360,10 +5365,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578088</v>
+        <v>578146</v>
       </c>
       <c r="R42" t="n">
-        <v>6340470</v>
+        <v>6340431</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5396,11 +5401,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5427,10 +5427,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124305419</v>
+        <v>124306142</v>
       </c>
       <c r="B43" t="n">
-        <v>95423</v>
+        <v>95705</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5443,21 +5443,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2671</v>
+        <v>2180</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577961</v>
+        <v>577937</v>
       </c>
       <c r="R43" t="n">
-        <v>6340362</v>
+        <v>6340345</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5529,10 +5529,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124796768</v>
+        <v>124795874</v>
       </c>
       <c r="B44" t="n">
-        <v>79428</v>
+        <v>79004</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5541,41 +5541,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>1639</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578118</v>
+        <v>578029</v>
       </c>
       <c r="R44" t="n">
-        <v>6340459</v>
+        <v>6340450</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5619,19 +5619,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124797831</v>
+        <v>124795772</v>
       </c>
       <c r="B45" t="n">
         <v>96354</v>
@@ -5671,13 +5671,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578055</v>
+        <v>578110</v>
       </c>
       <c r="R45" t="n">
-        <v>6340450</v>
+        <v>6340428</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5726,17 +5726,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124796185</v>
+        <v>124797764</v>
       </c>
       <c r="B46" t="n">
-        <v>79428</v>
+        <v>57666</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5749,37 +5749,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578013</v>
+        <v>578056</v>
       </c>
       <c r="R46" t="n">
-        <v>6340449</v>
+        <v>6340468</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5823,22 +5828,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124796245</v>
+        <v>124796460</v>
       </c>
       <c r="B47" t="n">
-        <v>79004</v>
+        <v>95423</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5851,37 +5856,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1639</v>
+        <v>2671</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577987</v>
+        <v>578092</v>
       </c>
       <c r="R47" t="n">
-        <v>6340434</v>
+        <v>6340465</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5925,22 +5930,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124795874</v>
+        <v>124795668</v>
       </c>
       <c r="B48" t="n">
-        <v>79004</v>
+        <v>91023</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5953,34 +5958,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1639</v>
+        <v>1205</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578029</v>
+        <v>578042</v>
       </c>
       <c r="R48" t="n">
-        <v>6340450</v>
+        <v>6340382</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6039,10 +6048,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124797728</v>
+        <v>124796060</v>
       </c>
       <c r="B49" t="n">
-        <v>57529</v>
+        <v>79428</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6055,37 +6064,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578047</v>
+        <v>578034</v>
       </c>
       <c r="R49" t="n">
-        <v>6340449</v>
+        <v>6340457</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6115,11 +6124,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6134,22 +6138,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124795621</v>
+        <v>124797648</v>
       </c>
       <c r="B50" t="n">
-        <v>57995</v>
+        <v>8447</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6158,50 +6162,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103018</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Boda, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578049</v>
+        <v>578060</v>
       </c>
       <c r="R50" t="n">
-        <v>6340376</v>
+        <v>6340459</v>
       </c>
       <c r="S50" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6231,6 +6226,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6245,22 +6245,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124797132</v>
+        <v>124795744</v>
       </c>
       <c r="B51" t="n">
-        <v>5196</v>
+        <v>79428</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6269,41 +6269,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>105930</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578099</v>
+        <v>578042</v>
       </c>
       <c r="R51" t="n">
-        <v>6340486</v>
+        <v>6340428</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6333,11 +6333,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6352,22 +6347,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124799230</v>
+        <v>124797132</v>
       </c>
       <c r="B52" t="n">
-        <v>92210</v>
+        <v>5196</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6376,41 +6371,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2075</v>
+        <v>105930</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577970</v>
+        <v>578099</v>
       </c>
       <c r="R52" t="n">
-        <v>6340397</v>
+        <v>6340486</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6440,6 +6435,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6454,22 +6454,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124795744</v>
+        <v>124797728</v>
       </c>
       <c r="B53" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6482,37 +6482,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578042</v>
+        <v>578047</v>
       </c>
       <c r="R53" t="n">
-        <v>6340428</v>
+        <v>6340449</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6542,6 +6542,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6556,22 +6561,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124797648</v>
+        <v>124796306</v>
       </c>
       <c r="B54" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6580,41 +6585,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578060</v>
+        <v>577987</v>
       </c>
       <c r="R54" t="n">
-        <v>6340459</v>
+        <v>6340434</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6644,11 +6649,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6663,22 +6663,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124795887</v>
+        <v>124796768</v>
       </c>
       <c r="B55" t="n">
-        <v>96390</v>
+        <v>79428</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6687,25 +6687,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2590</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578113</v>
+        <v>578118</v>
       </c>
       <c r="R55" t="n">
-        <v>6340445</v>
+        <v>6340459</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6777,10 +6777,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124797764</v>
+        <v>124796606</v>
       </c>
       <c r="B56" t="n">
-        <v>57666</v>
+        <v>92239</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6789,46 +6789,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>26</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578056</v>
+        <v>578096</v>
       </c>
       <c r="R56" t="n">
-        <v>6340468</v>
+        <v>6340479</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6877,17 +6872,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124795668</v>
+        <v>124796529</v>
       </c>
       <c r="B57" t="n">
-        <v>91023</v>
+        <v>79891</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6896,42 +6891,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578042</v>
+        <v>577974</v>
       </c>
       <c r="R57" t="n">
-        <v>6340382</v>
+        <v>6340427</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6990,10 +6981,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124795772</v>
+        <v>124796269</v>
       </c>
       <c r="B58" t="n">
-        <v>96354</v>
+        <v>5361</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7006,21 +6997,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>101728</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7030,13 +7021,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578110</v>
+        <v>578107</v>
       </c>
       <c r="R58" t="n">
-        <v>6340428</v>
+        <v>6340454</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7066,6 +7057,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7085,17 +7081,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124796060</v>
+        <v>124797831</v>
       </c>
       <c r="B59" t="n">
-        <v>79428</v>
+        <v>96354</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7108,37 +7104,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578034</v>
+        <v>578055</v>
       </c>
       <c r="R59" t="n">
-        <v>6340457</v>
+        <v>6340450</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7182,22 +7178,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124796306</v>
+        <v>124796245</v>
       </c>
       <c r="B60" t="n">
-        <v>79428</v>
+        <v>79004</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7206,25 +7202,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>1639</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7296,10 +7292,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124796606</v>
+        <v>124795887</v>
       </c>
       <c r="B61" t="n">
-        <v>92239</v>
+        <v>96390</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7312,21 +7308,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>26</v>
+        <v>2590</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7336,13 +7332,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578096</v>
+        <v>578113</v>
       </c>
       <c r="R61" t="n">
-        <v>6340479</v>
+        <v>6340445</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7398,10 +7394,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124796460</v>
+        <v>124796185</v>
       </c>
       <c r="B62" t="n">
-        <v>95423</v>
+        <v>79428</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7410,41 +7406,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2671</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578092</v>
+        <v>578013</v>
       </c>
       <c r="R62" t="n">
-        <v>6340465</v>
+        <v>6340449</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7488,22 +7484,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124796529</v>
+        <v>124799230</v>
       </c>
       <c r="B63" t="n">
-        <v>79891</v>
+        <v>92210</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7516,21 +7512,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>2075</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7540,10 +7536,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577974</v>
+        <v>577970</v>
       </c>
       <c r="R63" t="n">
-        <v>6340427</v>
+        <v>6340397</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7602,10 +7598,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124796269</v>
+        <v>124795621</v>
       </c>
       <c r="B64" t="n">
-        <v>5361</v>
+        <v>57995</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7618,37 +7614,46 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>101728</v>
+        <v>103018</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Mosse Hjortshult, Boda, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578107</v>
+        <v>578049</v>
       </c>
       <c r="R64" t="n">
-        <v>6340454</v>
+        <v>6340376</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7678,11 +7683,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7697,22 +7697,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124825677</v>
+        <v>124825657</v>
       </c>
       <c r="B65" t="n">
-        <v>96390</v>
+        <v>92210</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7721,31 +7721,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2590</v>
+        <v>2075</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7753,10 +7752,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>578131</v>
+        <v>577974</v>
       </c>
       <c r="R65" t="n">
-        <v>6340387</v>
+        <v>6340399</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7816,10 +7815,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124825691</v>
+        <v>124825677</v>
       </c>
       <c r="B66" t="n">
-        <v>4772</v>
+        <v>96390</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7832,28 +7831,27 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100299</v>
+        <v>2590</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7861,10 +7859,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578135</v>
+        <v>578131</v>
       </c>
       <c r="R66" t="n">
-        <v>6340398</v>
+        <v>6340387</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7897,11 +7895,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7929,10 +7922,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124825657</v>
+        <v>124825691</v>
       </c>
       <c r="B67" t="n">
-        <v>92210</v>
+        <v>4772</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7941,30 +7934,32 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2075</v>
+        <v>100299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7972,10 +7967,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>577974</v>
+        <v>578135</v>
       </c>
       <c r="R67" t="n">
-        <v>6340399</v>
+        <v>6340398</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8008,6 +8003,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -4597,10 +4597,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124303500</v>
+        <v>124307670</v>
       </c>
       <c r="B35" t="n">
-        <v>56722</v>
+        <v>95423</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4613,46 +4613,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>2671</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578140</v>
+        <v>578089</v>
       </c>
       <c r="R35" t="n">
-        <v>6340418</v>
+        <v>6340417</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4708,10 +4699,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124304628</v>
+        <v>124308072</v>
       </c>
       <c r="B36" t="n">
-        <v>95705</v>
+        <v>105117</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4724,21 +4715,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4748,13 +4739,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578054</v>
+        <v>578059</v>
       </c>
       <c r="R36" t="n">
-        <v>6340399</v>
+        <v>6340412</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4810,10 +4801,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124306409</v>
+        <v>124303584</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>91032</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4826,21 +4817,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4850,10 +4841,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577906</v>
+        <v>578146</v>
       </c>
       <c r="R37" t="n">
-        <v>6340336</v>
+        <v>6340431</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4912,10 +4903,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124307670</v>
+        <v>124306409</v>
       </c>
       <c r="B38" t="n">
-        <v>95423</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4924,25 +4915,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2671</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4952,13 +4943,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578089</v>
+        <v>577906</v>
       </c>
       <c r="R38" t="n">
-        <v>6340417</v>
+        <v>6340336</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5014,10 +5005,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124304453</v>
+        <v>124304628</v>
       </c>
       <c r="B39" t="n">
-        <v>57529</v>
+        <v>95705</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5026,25 +5017,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5054,13 +5045,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578088</v>
+        <v>578054</v>
       </c>
       <c r="R39" t="n">
-        <v>6340470</v>
+        <v>6340399</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5090,11 +5081,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5121,10 +5107,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124308072</v>
+        <v>124304453</v>
       </c>
       <c r="B40" t="n">
-        <v>105117</v>
+        <v>57529</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5133,25 +5119,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5161,10 +5147,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578059</v>
+        <v>578088</v>
       </c>
       <c r="R40" t="n">
-        <v>6340412</v>
+        <v>6340470</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5197,6 +5183,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5223,10 +5214,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124305419</v>
+        <v>124306142</v>
       </c>
       <c r="B41" t="n">
-        <v>95423</v>
+        <v>95705</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5239,21 +5230,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2671</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5263,10 +5254,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577961</v>
+        <v>577937</v>
       </c>
       <c r="R41" t="n">
-        <v>6340362</v>
+        <v>6340345</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5325,10 +5316,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124303584</v>
+        <v>124303500</v>
       </c>
       <c r="B42" t="n">
-        <v>91032</v>
+        <v>56722</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5337,41 +5328,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578146</v>
+        <v>578140</v>
       </c>
       <c r="R42" t="n">
-        <v>6340431</v>
+        <v>6340418</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5427,10 +5427,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124306142</v>
+        <v>124305419</v>
       </c>
       <c r="B43" t="n">
-        <v>95705</v>
+        <v>95423</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5443,21 +5443,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2180</v>
+        <v>2671</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577937</v>
+        <v>577961</v>
       </c>
       <c r="R43" t="n">
-        <v>6340345</v>
+        <v>6340362</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -7394,10 +7394,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124796185</v>
+        <v>124799230</v>
       </c>
       <c r="B62" t="n">
-        <v>79428</v>
+        <v>92210</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7410,21 +7410,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>2075</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578013</v>
+        <v>577970</v>
       </c>
       <c r="R62" t="n">
-        <v>6340449</v>
+        <v>6340397</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7496,10 +7496,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124799230</v>
+        <v>124796185</v>
       </c>
       <c r="B63" t="n">
-        <v>92210</v>
+        <v>79428</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7512,21 +7512,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2075</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577970</v>
+        <v>578013</v>
       </c>
       <c r="R63" t="n">
-        <v>6340397</v>
+        <v>6340449</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -5316,10 +5316,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124303500</v>
+        <v>124305419</v>
       </c>
       <c r="B42" t="n">
-        <v>56722</v>
+        <v>95423</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5332,46 +5332,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>2671</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578140</v>
+        <v>577961</v>
       </c>
       <c r="R42" t="n">
-        <v>6340418</v>
+        <v>6340362</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5427,10 +5418,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124305419</v>
+        <v>124303500</v>
       </c>
       <c r="B43" t="n">
-        <v>95423</v>
+        <v>56722</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5443,37 +5434,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2671</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577961</v>
+        <v>578140</v>
       </c>
       <c r="R43" t="n">
-        <v>6340362</v>
+        <v>6340418</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -7394,10 +7394,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124799230</v>
+        <v>124796185</v>
       </c>
       <c r="B62" t="n">
-        <v>92210</v>
+        <v>79428</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7410,21 +7410,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2075</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577970</v>
+        <v>578013</v>
       </c>
       <c r="R62" t="n">
-        <v>6340397</v>
+        <v>6340449</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7496,10 +7496,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124796185</v>
+        <v>124799230</v>
       </c>
       <c r="B63" t="n">
-        <v>79428</v>
+        <v>92210</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7512,21 +7512,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>2075</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578013</v>
+        <v>577970</v>
       </c>
       <c r="R63" t="n">
-        <v>6340449</v>
+        <v>6340397</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -5529,10 +5529,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124795874</v>
+        <v>124795772</v>
       </c>
       <c r="B44" t="n">
-        <v>79004</v>
+        <v>96354</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5541,41 +5541,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1639</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578029</v>
+        <v>578110</v>
       </c>
       <c r="R44" t="n">
-        <v>6340450</v>
+        <v>6340428</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5619,22 +5619,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124795772</v>
+        <v>124796306</v>
       </c>
       <c r="B45" t="n">
-        <v>96354</v>
+        <v>79428</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5647,37 +5647,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578110</v>
+        <v>577987</v>
       </c>
       <c r="R45" t="n">
-        <v>6340428</v>
+        <v>6340434</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5721,22 +5721,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124797764</v>
+        <v>124797831</v>
       </c>
       <c r="B46" t="n">
-        <v>57666</v>
+        <v>96354</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5749,42 +5749,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578056</v>
+        <v>578055</v>
       </c>
       <c r="R46" t="n">
-        <v>6340468</v>
+        <v>6340450</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5833,17 +5828,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124796460</v>
+        <v>124797648</v>
       </c>
       <c r="B47" t="n">
-        <v>95423</v>
+        <v>8447</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5856,21 +5851,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2671</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5880,13 +5875,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578092</v>
+        <v>578060</v>
       </c>
       <c r="R47" t="n">
-        <v>6340465</v>
+        <v>6340459</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5916,6 +5911,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5935,17 +5935,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124795668</v>
+        <v>124796460</v>
       </c>
       <c r="B48" t="n">
-        <v>91023</v>
+        <v>95423</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5958,41 +5958,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1205</v>
+        <v>2671</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578042</v>
+        <v>578092</v>
       </c>
       <c r="R48" t="n">
-        <v>6340382</v>
+        <v>6340465</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6036,22 +6032,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124796060</v>
+        <v>124796245</v>
       </c>
       <c r="B49" t="n">
-        <v>79428</v>
+        <v>79004</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6060,25 +6056,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>1639</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6088,10 +6084,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578034</v>
+        <v>577987</v>
       </c>
       <c r="R49" t="n">
-        <v>6340457</v>
+        <v>6340434</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6150,10 +6146,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124797648</v>
+        <v>124795874</v>
       </c>
       <c r="B50" t="n">
-        <v>8447</v>
+        <v>79004</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6166,37 +6162,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>1639</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578060</v>
+        <v>578029</v>
       </c>
       <c r="R50" t="n">
-        <v>6340459</v>
+        <v>6340450</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6226,11 +6222,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6245,22 +6236,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124795744</v>
+        <v>124797728</v>
       </c>
       <c r="B51" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6273,37 +6264,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578042</v>
+        <v>578047</v>
       </c>
       <c r="R51" t="n">
-        <v>6340428</v>
+        <v>6340449</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6333,6 +6324,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6347,22 +6343,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124797132</v>
+        <v>124797764</v>
       </c>
       <c r="B52" t="n">
-        <v>5196</v>
+        <v>57666</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6371,41 +6367,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578099</v>
+        <v>578056</v>
       </c>
       <c r="R52" t="n">
-        <v>6340486</v>
+        <v>6340468</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6435,11 +6436,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6459,17 +6455,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124797728</v>
+        <v>124796606</v>
       </c>
       <c r="B53" t="n">
-        <v>57529</v>
+        <v>92239</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6478,25 +6474,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>26</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6506,10 +6502,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578047</v>
+        <v>578096</v>
       </c>
       <c r="R53" t="n">
-        <v>6340449</v>
+        <v>6340479</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6542,11 +6538,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6573,10 +6564,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124796306</v>
+        <v>124796529</v>
       </c>
       <c r="B54" t="n">
-        <v>79428</v>
+        <v>79891</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6589,21 +6580,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6613,10 +6604,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577987</v>
+        <v>577974</v>
       </c>
       <c r="R54" t="n">
-        <v>6340434</v>
+        <v>6340427</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6777,10 +6768,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124796606</v>
+        <v>124795621</v>
       </c>
       <c r="B56" t="n">
-        <v>92239</v>
+        <v>57995</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6789,41 +6780,50 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>26</v>
+        <v>103018</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Mosse Hjortshult, Boda, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578096</v>
+        <v>578049</v>
       </c>
       <c r="R56" t="n">
-        <v>6340479</v>
+        <v>6340376</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6867,22 +6867,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124796529</v>
+        <v>124796060</v>
       </c>
       <c r="B57" t="n">
-        <v>79891</v>
+        <v>79428</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6895,21 +6895,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>577974</v>
+        <v>578034</v>
       </c>
       <c r="R57" t="n">
-        <v>6340427</v>
+        <v>6340457</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6981,10 +6981,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124796269</v>
+        <v>124799230</v>
       </c>
       <c r="B58" t="n">
-        <v>5361</v>
+        <v>92210</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6997,37 +6997,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>101728</v>
+        <v>2075</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578107</v>
+        <v>577970</v>
       </c>
       <c r="R58" t="n">
-        <v>6340454</v>
+        <v>6340397</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7057,11 +7057,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7076,22 +7071,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124797831</v>
+        <v>124797132</v>
       </c>
       <c r="B59" t="n">
-        <v>96354</v>
+        <v>5196</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7100,25 +7095,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7128,10 +7123,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578055</v>
+        <v>578099</v>
       </c>
       <c r="R59" t="n">
-        <v>6340450</v>
+        <v>6340486</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7164,6 +7159,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7190,10 +7190,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124796245</v>
+        <v>124796269</v>
       </c>
       <c r="B60" t="n">
-        <v>79004</v>
+        <v>5361</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7202,41 +7202,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1639</v>
+        <v>101728</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577987</v>
+        <v>578107</v>
       </c>
       <c r="R60" t="n">
-        <v>6340434</v>
+        <v>6340454</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7266,6 +7266,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7280,22 +7285,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124795887</v>
+        <v>124795668</v>
       </c>
       <c r="B61" t="n">
-        <v>96390</v>
+        <v>91023</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7308,37 +7313,41 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2590</v>
+        <v>1205</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578113</v>
+        <v>578042</v>
       </c>
       <c r="R61" t="n">
-        <v>6340445</v>
+        <v>6340382</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7382,19 +7391,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124796185</v>
+        <v>124795744</v>
       </c>
       <c r="B62" t="n">
         <v>79428</v>
@@ -7430,14 +7439,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578013</v>
+        <v>578042</v>
       </c>
       <c r="R62" t="n">
-        <v>6340449</v>
+        <v>6340428</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7496,10 +7505,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124799230</v>
+        <v>124795887</v>
       </c>
       <c r="B63" t="n">
-        <v>92210</v>
+        <v>96390</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7508,41 +7517,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2075</v>
+        <v>2590</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577970</v>
+        <v>578113</v>
       </c>
       <c r="R63" t="n">
-        <v>6340397</v>
+        <v>6340445</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7586,22 +7595,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124795621</v>
+        <v>124796185</v>
       </c>
       <c r="B64" t="n">
-        <v>57995</v>
+        <v>79428</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7614,46 +7623,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103018</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Boda, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578049</v>
+        <v>578013</v>
       </c>
       <c r="R64" t="n">
-        <v>6340376</v>
+        <v>6340449</v>
       </c>
       <c r="S64" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7815,10 +7815,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124825677</v>
+        <v>124825691</v>
       </c>
       <c r="B66" t="n">
-        <v>96390</v>
+        <v>4772</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7831,27 +7831,28 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2590</v>
+        <v>100299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7859,10 +7860,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578131</v>
+        <v>578135</v>
       </c>
       <c r="R66" t="n">
-        <v>6340387</v>
+        <v>6340398</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7895,6 +7896,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7922,10 +7928,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124825691</v>
+        <v>124825677</v>
       </c>
       <c r="B67" t="n">
-        <v>4772</v>
+        <v>96390</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7938,28 +7944,27 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100299</v>
+        <v>2590</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7967,10 +7972,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>578135</v>
+        <v>578131</v>
       </c>
       <c r="R67" t="n">
-        <v>6340398</v>
+        <v>6340387</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8003,11 +8008,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -5529,10 +5529,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124795772</v>
+        <v>124796768</v>
       </c>
       <c r="B44" t="n">
-        <v>96354</v>
+        <v>79428</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578110</v>
+        <v>578118</v>
       </c>
       <c r="R44" t="n">
-        <v>6340428</v>
+        <v>6340459</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5624,17 +5624,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124796306</v>
+        <v>124795887</v>
       </c>
       <c r="B45" t="n">
-        <v>79428</v>
+        <v>96390</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5643,41 +5643,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>2590</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577987</v>
+        <v>578113</v>
       </c>
       <c r="R45" t="n">
-        <v>6340434</v>
+        <v>6340445</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5721,22 +5721,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124797831</v>
+        <v>124796306</v>
       </c>
       <c r="B46" t="n">
-        <v>96354</v>
+        <v>79428</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5749,37 +5749,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578055</v>
+        <v>577987</v>
       </c>
       <c r="R46" t="n">
-        <v>6340450</v>
+        <v>6340434</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5823,22 +5823,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124797648</v>
+        <v>124796185</v>
       </c>
       <c r="B47" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5847,41 +5847,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578060</v>
+        <v>578013</v>
       </c>
       <c r="R47" t="n">
-        <v>6340459</v>
+        <v>6340449</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5911,11 +5911,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5930,22 +5925,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124796460</v>
+        <v>124795744</v>
       </c>
       <c r="B48" t="n">
-        <v>95423</v>
+        <v>79428</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5954,41 +5949,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2671</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578092</v>
+        <v>578042</v>
       </c>
       <c r="R48" t="n">
-        <v>6340465</v>
+        <v>6340428</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6032,22 +6027,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124796245</v>
+        <v>124799230</v>
       </c>
       <c r="B49" t="n">
-        <v>79004</v>
+        <v>92210</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6056,25 +6051,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1639</v>
+        <v>2075</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6084,10 +6079,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577987</v>
+        <v>577970</v>
       </c>
       <c r="R49" t="n">
-        <v>6340434</v>
+        <v>6340397</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6146,10 +6141,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124795874</v>
+        <v>124795668</v>
       </c>
       <c r="B50" t="n">
-        <v>79004</v>
+        <v>91023</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6162,34 +6157,38 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1639</v>
+        <v>1205</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578029</v>
+        <v>578042</v>
       </c>
       <c r="R50" t="n">
-        <v>6340450</v>
+        <v>6340382</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6248,10 +6247,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124797728</v>
+        <v>124797648</v>
       </c>
       <c r="B51" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6260,25 +6259,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6288,10 +6287,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578047</v>
+        <v>578060</v>
       </c>
       <c r="R51" t="n">
-        <v>6340449</v>
+        <v>6340459</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6328,7 +6327,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6348,17 +6347,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124797764</v>
+        <v>124796606</v>
       </c>
       <c r="B52" t="n">
-        <v>57666</v>
+        <v>92239</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6367,46 +6366,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>26</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578056</v>
+        <v>578096</v>
       </c>
       <c r="R52" t="n">
-        <v>6340468</v>
+        <v>6340479</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6455,17 +6449,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124796606</v>
+        <v>124795874</v>
       </c>
       <c r="B53" t="n">
-        <v>92239</v>
+        <v>79004</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6478,37 +6472,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>26</v>
+        <v>1639</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578096</v>
+        <v>578029</v>
       </c>
       <c r="R53" t="n">
-        <v>6340479</v>
+        <v>6340450</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6552,12 +6546,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6666,10 +6660,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124796768</v>
+        <v>124797831</v>
       </c>
       <c r="B55" t="n">
-        <v>79428</v>
+        <v>96354</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6682,21 +6676,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6706,13 +6700,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578118</v>
+        <v>578055</v>
       </c>
       <c r="R55" t="n">
-        <v>6340459</v>
+        <v>6340450</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6768,10 +6762,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124795621</v>
+        <v>124795772</v>
       </c>
       <c r="B56" t="n">
-        <v>57995</v>
+        <v>96354</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6784,46 +6778,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103018</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Boda, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578049</v>
+        <v>578110</v>
       </c>
       <c r="R56" t="n">
-        <v>6340376</v>
+        <v>6340428</v>
       </c>
       <c r="S56" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6867,22 +6852,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124796060</v>
+        <v>124796245</v>
       </c>
       <c r="B57" t="n">
-        <v>79428</v>
+        <v>79004</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6891,25 +6876,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>1639</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6919,10 +6904,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578034</v>
+        <v>577987</v>
       </c>
       <c r="R57" t="n">
-        <v>6340457</v>
+        <v>6340434</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6981,10 +6966,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124799230</v>
+        <v>124795621</v>
       </c>
       <c r="B58" t="n">
-        <v>92210</v>
+        <v>57995</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6997,37 +6982,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2075</v>
+        <v>103018</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Mosse Hjortshult, Boda, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>577970</v>
+        <v>578049</v>
       </c>
       <c r="R58" t="n">
-        <v>6340397</v>
+        <v>6340376</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7083,10 +7077,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124797132</v>
+        <v>124797764</v>
       </c>
       <c r="B59" t="n">
-        <v>5196</v>
+        <v>57666</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7095,41 +7089,46 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578099</v>
+        <v>578056</v>
       </c>
       <c r="R59" t="n">
-        <v>6340486</v>
+        <v>6340468</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7159,11 +7158,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7183,17 +7177,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124796269</v>
+        <v>124797132</v>
       </c>
       <c r="B60" t="n">
-        <v>5361</v>
+        <v>5196</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7202,25 +7196,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>101728</v>
+        <v>105930</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7230,10 +7224,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578107</v>
+        <v>578099</v>
       </c>
       <c r="R60" t="n">
-        <v>6340454</v>
+        <v>6340486</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7270,7 +7264,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Kläckhål</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7297,10 +7291,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124795668</v>
+        <v>124796460</v>
       </c>
       <c r="B61" t="n">
-        <v>91023</v>
+        <v>95423</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7313,41 +7307,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1205</v>
+        <v>2671</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578042</v>
+        <v>578092</v>
       </c>
       <c r="R61" t="n">
-        <v>6340382</v>
+        <v>6340465</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7391,22 +7381,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124795744</v>
+        <v>124797728</v>
       </c>
       <c r="B62" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7419,37 +7409,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578042</v>
+        <v>578047</v>
       </c>
       <c r="R62" t="n">
-        <v>6340428</v>
+        <v>6340449</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7479,6 +7469,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7493,22 +7488,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124795887</v>
+        <v>124796269</v>
       </c>
       <c r="B63" t="n">
-        <v>96390</v>
+        <v>5361</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7517,25 +7512,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2590</v>
+        <v>101728</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7545,13 +7540,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578113</v>
+        <v>578107</v>
       </c>
       <c r="R63" t="n">
-        <v>6340445</v>
+        <v>6340454</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7581,6 +7576,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7607,7 +7607,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124796185</v>
+        <v>124796060</v>
       </c>
       <c r="B64" t="n">
         <v>79428</v>
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578013</v>
+        <v>578034</v>
       </c>
       <c r="R64" t="n">
-        <v>6340449</v>
+        <v>6340457</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7709,10 +7709,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124825657</v>
+        <v>124825677</v>
       </c>
       <c r="B65" t="n">
-        <v>92210</v>
+        <v>96390</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7721,30 +7721,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2075</v>
+        <v>2590</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7752,10 +7753,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>577974</v>
+        <v>578131</v>
       </c>
       <c r="R65" t="n">
-        <v>6340399</v>
+        <v>6340387</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7928,10 +7929,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124825677</v>
+        <v>124825657</v>
       </c>
       <c r="B67" t="n">
-        <v>96390</v>
+        <v>92210</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7940,31 +7941,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2590</v>
+        <v>2075</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7972,10 +7972,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>578131</v>
+        <v>577974</v>
       </c>
       <c r="R67" t="n">
-        <v>6340387</v>
+        <v>6340399</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -5631,10 +5631,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124795887</v>
+        <v>124795874</v>
       </c>
       <c r="B45" t="n">
-        <v>96390</v>
+        <v>79004</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5647,37 +5647,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2590</v>
+        <v>1639</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578113</v>
+        <v>578029</v>
       </c>
       <c r="R45" t="n">
-        <v>6340445</v>
+        <v>6340450</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5721,22 +5721,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124796306</v>
+        <v>124797648</v>
       </c>
       <c r="B46" t="n">
-        <v>79428</v>
+        <v>8447</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5745,41 +5745,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577987</v>
+        <v>578060</v>
       </c>
       <c r="R46" t="n">
-        <v>6340434</v>
+        <v>6340459</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5809,6 +5809,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5823,22 +5828,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124796185</v>
+        <v>124795668</v>
       </c>
       <c r="B47" t="n">
-        <v>79428</v>
+        <v>91023</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5847,38 +5852,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>1205</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578013</v>
+        <v>578042</v>
       </c>
       <c r="R47" t="n">
-        <v>6340449</v>
+        <v>6340382</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5937,10 +5946,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124795744</v>
+        <v>124797831</v>
       </c>
       <c r="B48" t="n">
-        <v>79428</v>
+        <v>96354</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5953,37 +5962,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578042</v>
+        <v>578055</v>
       </c>
       <c r="R48" t="n">
-        <v>6340428</v>
+        <v>6340450</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6027,22 +6036,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124799230</v>
+        <v>124796185</v>
       </c>
       <c r="B49" t="n">
-        <v>92210</v>
+        <v>79428</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6055,21 +6064,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2075</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6079,10 +6088,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577970</v>
+        <v>578013</v>
       </c>
       <c r="R49" t="n">
-        <v>6340397</v>
+        <v>6340449</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6141,10 +6150,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124795668</v>
+        <v>124796060</v>
       </c>
       <c r="B50" t="n">
-        <v>91023</v>
+        <v>79428</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6153,42 +6162,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1205</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578042</v>
+        <v>578034</v>
       </c>
       <c r="R50" t="n">
-        <v>6340382</v>
+        <v>6340457</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6247,10 +6252,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124797648</v>
+        <v>124795887</v>
       </c>
       <c r="B51" t="n">
-        <v>8447</v>
+        <v>96390</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6263,21 +6268,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6287,13 +6292,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578060</v>
+        <v>578113</v>
       </c>
       <c r="R51" t="n">
-        <v>6340459</v>
+        <v>6340445</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6323,11 +6328,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6347,17 +6347,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124796606</v>
+        <v>124796245</v>
       </c>
       <c r="B52" t="n">
-        <v>92239</v>
+        <v>79004</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6370,37 +6370,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>26</v>
+        <v>1639</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578096</v>
+        <v>577987</v>
       </c>
       <c r="R52" t="n">
-        <v>6340479</v>
+        <v>6340434</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6444,22 +6444,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124795874</v>
+        <v>124799230</v>
       </c>
       <c r="B53" t="n">
-        <v>79004</v>
+        <v>92210</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6468,38 +6468,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1639</v>
+        <v>2075</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578029</v>
+        <v>577970</v>
       </c>
       <c r="R53" t="n">
-        <v>6340450</v>
+        <v>6340397</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6558,10 +6558,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124796529</v>
+        <v>124795621</v>
       </c>
       <c r="B54" t="n">
-        <v>79891</v>
+        <v>57995</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6574,37 +6574,46 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>103018</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Mosse Hjortshult, Boda, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577974</v>
+        <v>578049</v>
       </c>
       <c r="R54" t="n">
-        <v>6340427</v>
+        <v>6340376</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6660,7 +6669,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124797831</v>
+        <v>124795772</v>
       </c>
       <c r="B55" t="n">
         <v>96354</v>
@@ -6700,13 +6709,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578055</v>
+        <v>578110</v>
       </c>
       <c r="R55" t="n">
-        <v>6340450</v>
+        <v>6340428</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6755,17 +6764,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124795772</v>
+        <v>124796460</v>
       </c>
       <c r="B56" t="n">
-        <v>96354</v>
+        <v>95423</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6774,25 +6783,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>2671</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6802,10 +6811,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578110</v>
+        <v>578092</v>
       </c>
       <c r="R56" t="n">
-        <v>6340428</v>
+        <v>6340465</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6857,17 +6866,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124796245</v>
+        <v>124797728</v>
       </c>
       <c r="B57" t="n">
-        <v>79004</v>
+        <v>57529</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6876,41 +6885,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1639</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>577987</v>
+        <v>578047</v>
       </c>
       <c r="R57" t="n">
-        <v>6340434</v>
+        <v>6340449</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6940,6 +6949,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6954,22 +6968,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124795621</v>
+        <v>124795744</v>
       </c>
       <c r="B58" t="n">
-        <v>57995</v>
+        <v>79428</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6982,46 +6996,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103018</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Boda, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578049</v>
+        <v>578042</v>
       </c>
       <c r="R58" t="n">
-        <v>6340376</v>
+        <v>6340428</v>
       </c>
       <c r="S58" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7077,10 +7082,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124797764</v>
+        <v>124797132</v>
       </c>
       <c r="B59" t="n">
-        <v>57666</v>
+        <v>5196</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7089,46 +7094,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>105930</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578056</v>
+        <v>578099</v>
       </c>
       <c r="R59" t="n">
-        <v>6340468</v>
+        <v>6340486</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7158,6 +7158,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7177,17 +7182,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124797132</v>
+        <v>124796306</v>
       </c>
       <c r="B60" t="n">
-        <v>5196</v>
+        <v>79428</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7196,41 +7201,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>105930</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578099</v>
+        <v>577987</v>
       </c>
       <c r="R60" t="n">
-        <v>6340486</v>
+        <v>6340434</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7260,11 +7265,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7279,22 +7279,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124796460</v>
+        <v>124796606</v>
       </c>
       <c r="B61" t="n">
-        <v>95423</v>
+        <v>92239</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7307,21 +7307,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2671</v>
+        <v>26</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7331,13 +7331,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578092</v>
+        <v>578096</v>
       </c>
       <c r="R61" t="n">
-        <v>6340465</v>
+        <v>6340479</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7393,10 +7393,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124797728</v>
+        <v>124796269</v>
       </c>
       <c r="B62" t="n">
-        <v>57529</v>
+        <v>5361</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7409,21 +7409,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7433,10 +7433,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578047</v>
+        <v>578107</v>
       </c>
       <c r="R62" t="n">
-        <v>6340449</v>
+        <v>6340454</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7500,10 +7500,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124796269</v>
+        <v>124796529</v>
       </c>
       <c r="B63" t="n">
-        <v>5361</v>
+        <v>79891</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7516,37 +7516,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>101728</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578107</v>
+        <v>577974</v>
       </c>
       <c r="R63" t="n">
-        <v>6340454</v>
+        <v>6340427</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7576,11 +7576,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7595,22 +7590,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124796060</v>
+        <v>124797764</v>
       </c>
       <c r="B64" t="n">
-        <v>79428</v>
+        <v>57666</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7623,37 +7618,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578034</v>
+        <v>578056</v>
       </c>
       <c r="R64" t="n">
-        <v>6340457</v>
+        <v>6340468</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7697,22 +7697,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124825677</v>
+        <v>124825657</v>
       </c>
       <c r="B65" t="n">
-        <v>96390</v>
+        <v>92210</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7721,31 +7721,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2590</v>
+        <v>2075</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7753,10 +7752,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>578131</v>
+        <v>577974</v>
       </c>
       <c r="R65" t="n">
-        <v>6340387</v>
+        <v>6340399</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7816,10 +7815,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124825691</v>
+        <v>124825677</v>
       </c>
       <c r="B66" t="n">
-        <v>4772</v>
+        <v>96390</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7832,28 +7831,27 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100299</v>
+        <v>2590</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7861,10 +7859,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578135</v>
+        <v>578131</v>
       </c>
       <c r="R66" t="n">
-        <v>6340398</v>
+        <v>6340387</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7897,11 +7895,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7929,10 +7922,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124825657</v>
+        <v>124825691</v>
       </c>
       <c r="B67" t="n">
-        <v>92210</v>
+        <v>4772</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7941,30 +7934,32 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2075</v>
+        <v>100299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7972,10 +7967,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>577974</v>
+        <v>578135</v>
       </c>
       <c r="R67" t="n">
-        <v>6340399</v>
+        <v>6340398</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8008,6 +8003,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -5733,10 +5733,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124797648</v>
+        <v>124797831</v>
       </c>
       <c r="B46" t="n">
-        <v>8447</v>
+        <v>96354</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5745,25 +5745,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5773,10 +5773,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578060</v>
+        <v>578055</v>
       </c>
       <c r="R46" t="n">
-        <v>6340459</v>
+        <v>6340450</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5811,11 +5811,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Spår och kläckhål</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5833,7 +5828,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5946,10 +5941,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124797831</v>
+        <v>124796185</v>
       </c>
       <c r="B48" t="n">
-        <v>96354</v>
+        <v>79428</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5962,37 +5957,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578055</v>
+        <v>578013</v>
       </c>
       <c r="R48" t="n">
-        <v>6340450</v>
+        <v>6340449</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6036,19 +6031,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124796185</v>
+        <v>124796060</v>
       </c>
       <c r="B49" t="n">
         <v>79428</v>
@@ -6088,10 +6083,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578013</v>
+        <v>578034</v>
       </c>
       <c r="R49" t="n">
-        <v>6340449</v>
+        <v>6340457</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6150,10 +6145,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124796060</v>
+        <v>124797648</v>
       </c>
       <c r="B50" t="n">
-        <v>79428</v>
+        <v>8447</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6162,41 +6157,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578034</v>
+        <v>578060</v>
       </c>
       <c r="R50" t="n">
-        <v>6340457</v>
+        <v>6340459</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6226,6 +6221,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6240,12 +6240,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6669,10 +6669,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124795772</v>
+        <v>124796460</v>
       </c>
       <c r="B55" t="n">
-        <v>96354</v>
+        <v>95423</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6681,25 +6681,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>2671</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578110</v>
+        <v>578092</v>
       </c>
       <c r="R55" t="n">
-        <v>6340428</v>
+        <v>6340465</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6764,17 +6764,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124796460</v>
+        <v>124795772</v>
       </c>
       <c r="B56" t="n">
-        <v>95423</v>
+        <v>96354</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6783,25 +6783,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2671</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578092</v>
+        <v>578110</v>
       </c>
       <c r="R56" t="n">
-        <v>6340465</v>
+        <v>6340428</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6866,17 +6866,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124797728</v>
+        <v>124795744</v>
       </c>
       <c r="B57" t="n">
-        <v>57529</v>
+        <v>79428</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6889,37 +6889,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578047</v>
+        <v>578042</v>
       </c>
       <c r="R57" t="n">
-        <v>6340449</v>
+        <v>6340428</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6949,11 +6949,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6968,22 +6963,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124795744</v>
+        <v>124797728</v>
       </c>
       <c r="B58" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6996,37 +6991,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578042</v>
+        <v>578047</v>
       </c>
       <c r="R58" t="n">
-        <v>6340428</v>
+        <v>6340449</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7056,6 +7051,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7070,12 +7070,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -5529,10 +5529,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124796768</v>
+        <v>124795887</v>
       </c>
       <c r="B44" t="n">
-        <v>79428</v>
+        <v>96390</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5541,25 +5541,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>2590</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578118</v>
+        <v>578113</v>
       </c>
       <c r="R44" t="n">
-        <v>6340459</v>
+        <v>6340445</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5631,10 +5631,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124795874</v>
+        <v>124797728</v>
       </c>
       <c r="B45" t="n">
-        <v>79004</v>
+        <v>57529</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5643,41 +5643,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1639</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578029</v>
+        <v>578047</v>
       </c>
       <c r="R45" t="n">
-        <v>6340450</v>
+        <v>6340449</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5707,6 +5707,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5721,22 +5726,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124797831</v>
+        <v>124796185</v>
       </c>
       <c r="B46" t="n">
-        <v>96354</v>
+        <v>79428</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5749,37 +5754,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578055</v>
+        <v>578013</v>
       </c>
       <c r="R46" t="n">
-        <v>6340450</v>
+        <v>6340449</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5823,22 +5828,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124795668</v>
+        <v>124797764</v>
       </c>
       <c r="B47" t="n">
-        <v>91023</v>
+        <v>57666</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5847,45 +5852,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1205</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578042</v>
+        <v>578056</v>
       </c>
       <c r="R47" t="n">
-        <v>6340382</v>
+        <v>6340468</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5929,22 +5935,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124796185</v>
+        <v>124795621</v>
       </c>
       <c r="B48" t="n">
-        <v>79428</v>
+        <v>57995</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5957,37 +5963,46 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>103018</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Mosse Hjortshult, Boda, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578013</v>
+        <v>578049</v>
       </c>
       <c r="R48" t="n">
-        <v>6340449</v>
+        <v>6340376</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6043,7 +6058,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124796060</v>
+        <v>124795744</v>
       </c>
       <c r="B49" t="n">
         <v>79428</v>
@@ -6079,14 +6094,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578034</v>
+        <v>578042</v>
       </c>
       <c r="R49" t="n">
-        <v>6340457</v>
+        <v>6340428</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6145,10 +6160,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124797648</v>
+        <v>124795772</v>
       </c>
       <c r="B50" t="n">
-        <v>8447</v>
+        <v>96354</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6157,25 +6172,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6185,13 +6200,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578060</v>
+        <v>578110</v>
       </c>
       <c r="R50" t="n">
-        <v>6340459</v>
+        <v>6340428</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6221,11 +6236,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6252,10 +6262,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124795887</v>
+        <v>124797648</v>
       </c>
       <c r="B51" t="n">
-        <v>96390</v>
+        <v>8447</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6268,21 +6278,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6292,13 +6302,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578113</v>
+        <v>578060</v>
       </c>
       <c r="R51" t="n">
-        <v>6340445</v>
+        <v>6340459</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6328,6 +6338,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6347,17 +6362,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124796245</v>
+        <v>124795668</v>
       </c>
       <c r="B52" t="n">
-        <v>79004</v>
+        <v>91023</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6370,34 +6385,38 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1639</v>
+        <v>1205</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577987</v>
+        <v>578042</v>
       </c>
       <c r="R52" t="n">
-        <v>6340434</v>
+        <v>6340382</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6456,10 +6475,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124799230</v>
+        <v>124795874</v>
       </c>
       <c r="B53" t="n">
-        <v>92210</v>
+        <v>79004</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6468,38 +6487,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2075</v>
+        <v>1639</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577970</v>
+        <v>578029</v>
       </c>
       <c r="R53" t="n">
-        <v>6340397</v>
+        <v>6340450</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6558,10 +6577,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124795621</v>
+        <v>124796269</v>
       </c>
       <c r="B54" t="n">
-        <v>57995</v>
+        <v>5361</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6574,46 +6593,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103018</v>
+        <v>101728</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Boda, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578049</v>
+        <v>578107</v>
       </c>
       <c r="R54" t="n">
-        <v>6340376</v>
+        <v>6340454</v>
       </c>
       <c r="S54" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6643,6 +6653,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6657,22 +6672,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124796460</v>
+        <v>124796060</v>
       </c>
       <c r="B55" t="n">
-        <v>95423</v>
+        <v>79428</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6681,41 +6696,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2671</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578092</v>
+        <v>578034</v>
       </c>
       <c r="R55" t="n">
-        <v>6340465</v>
+        <v>6340457</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6759,22 +6774,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124795772</v>
+        <v>124797132</v>
       </c>
       <c r="B56" t="n">
-        <v>96354</v>
+        <v>5196</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6783,25 +6798,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6811,13 +6826,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578110</v>
+        <v>578099</v>
       </c>
       <c r="R56" t="n">
-        <v>6340428</v>
+        <v>6340486</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6847,6 +6862,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6866,17 +6886,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124795744</v>
+        <v>124796460</v>
       </c>
       <c r="B57" t="n">
-        <v>79428</v>
+        <v>95423</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6885,41 +6905,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>2671</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578042</v>
+        <v>578092</v>
       </c>
       <c r="R57" t="n">
-        <v>6340428</v>
+        <v>6340465</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6963,22 +6983,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124797728</v>
+        <v>124799230</v>
       </c>
       <c r="B58" t="n">
-        <v>57529</v>
+        <v>92210</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6991,37 +7011,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>2075</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578047</v>
+        <v>577970</v>
       </c>
       <c r="R58" t="n">
-        <v>6340449</v>
+        <v>6340397</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7051,11 +7071,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7070,22 +7085,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124797132</v>
+        <v>124796768</v>
       </c>
       <c r="B59" t="n">
-        <v>5196</v>
+        <v>79428</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7094,25 +7109,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>105930</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7122,13 +7137,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578099</v>
+        <v>578118</v>
       </c>
       <c r="R59" t="n">
-        <v>6340486</v>
+        <v>6340459</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7158,11 +7173,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7189,10 +7199,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124796306</v>
+        <v>124796606</v>
       </c>
       <c r="B60" t="n">
-        <v>79428</v>
+        <v>92239</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7201,41 +7211,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>26</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577987</v>
+        <v>578096</v>
       </c>
       <c r="R60" t="n">
-        <v>6340434</v>
+        <v>6340479</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7279,22 +7289,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124796606</v>
+        <v>124797831</v>
       </c>
       <c r="B61" t="n">
-        <v>92239</v>
+        <v>96354</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7303,25 +7313,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7331,10 +7341,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578096</v>
+        <v>578055</v>
       </c>
       <c r="R61" t="n">
-        <v>6340479</v>
+        <v>6340450</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7393,10 +7403,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124796269</v>
+        <v>124796529</v>
       </c>
       <c r="B62" t="n">
-        <v>5361</v>
+        <v>79891</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7409,37 +7419,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>101728</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578107</v>
+        <v>577974</v>
       </c>
       <c r="R62" t="n">
-        <v>6340454</v>
+        <v>6340427</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7469,11 +7479,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7488,22 +7493,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124796529</v>
+        <v>124796306</v>
       </c>
       <c r="B63" t="n">
-        <v>79891</v>
+        <v>79428</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7516,21 +7521,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7540,10 +7545,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577974</v>
+        <v>577987</v>
       </c>
       <c r="R63" t="n">
-        <v>6340427</v>
+        <v>6340434</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7602,10 +7607,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124797764</v>
+        <v>124796245</v>
       </c>
       <c r="B64" t="n">
-        <v>57666</v>
+        <v>79004</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7614,46 +7619,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>1639</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578056</v>
+        <v>577987</v>
       </c>
       <c r="R64" t="n">
-        <v>6340468</v>
+        <v>6340434</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7697,12 +7697,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -6160,10 +6160,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124795772</v>
+        <v>124797648</v>
       </c>
       <c r="B50" t="n">
-        <v>96354</v>
+        <v>8447</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6172,25 +6172,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6200,13 +6200,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578110</v>
+        <v>578060</v>
       </c>
       <c r="R50" t="n">
-        <v>6340428</v>
+        <v>6340459</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6236,6 +6236,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6262,10 +6267,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124797648</v>
+        <v>124795772</v>
       </c>
       <c r="B51" t="n">
-        <v>8447</v>
+        <v>96354</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6274,25 +6279,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6302,13 +6307,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578060</v>
+        <v>578110</v>
       </c>
       <c r="R51" t="n">
-        <v>6340459</v>
+        <v>6340428</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6338,11 +6343,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -5529,10 +5529,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124795887</v>
+        <v>124795772</v>
       </c>
       <c r="B44" t="n">
-        <v>96390</v>
+        <v>96354</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5541,25 +5541,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578113</v>
+        <v>578110</v>
       </c>
       <c r="R44" t="n">
-        <v>6340445</v>
+        <v>6340428</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5624,17 +5624,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124797728</v>
+        <v>124795744</v>
       </c>
       <c r="B45" t="n">
-        <v>57529</v>
+        <v>79428</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5647,37 +5647,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578047</v>
+        <v>578042</v>
       </c>
       <c r="R45" t="n">
-        <v>6340449</v>
+        <v>6340428</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5707,11 +5707,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5726,22 +5721,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124796185</v>
+        <v>124796529</v>
       </c>
       <c r="B46" t="n">
-        <v>79428</v>
+        <v>79891</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5754,21 +5749,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5778,10 +5773,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578013</v>
+        <v>577974</v>
       </c>
       <c r="R46" t="n">
-        <v>6340449</v>
+        <v>6340427</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5840,10 +5835,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124797764</v>
+        <v>124796306</v>
       </c>
       <c r="B47" t="n">
-        <v>57666</v>
+        <v>79428</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5856,42 +5851,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578056</v>
+        <v>577987</v>
       </c>
       <c r="R47" t="n">
-        <v>6340468</v>
+        <v>6340434</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5935,12 +5925,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6058,10 +6048,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124795744</v>
+        <v>124796606</v>
       </c>
       <c r="B49" t="n">
-        <v>79428</v>
+        <v>92239</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6070,41 +6060,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>26</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578042</v>
+        <v>578096</v>
       </c>
       <c r="R49" t="n">
-        <v>6340428</v>
+        <v>6340479</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6148,22 +6138,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124797648</v>
+        <v>124796768</v>
       </c>
       <c r="B50" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6172,25 +6162,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6200,13 +6190,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578060</v>
+        <v>578118</v>
       </c>
       <c r="R50" t="n">
         <v>6340459</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6236,11 +6226,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6260,17 +6245,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124795772</v>
+        <v>124795887</v>
       </c>
       <c r="B51" t="n">
-        <v>96354</v>
+        <v>96390</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6279,25 +6264,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6307,10 +6292,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578110</v>
+        <v>578113</v>
       </c>
       <c r="R51" t="n">
-        <v>6340428</v>
+        <v>6340445</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6362,17 +6347,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124795668</v>
+        <v>124797831</v>
       </c>
       <c r="B52" t="n">
-        <v>91023</v>
+        <v>96354</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6381,45 +6366,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1205</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578042</v>
+        <v>578055</v>
       </c>
       <c r="R52" t="n">
-        <v>6340382</v>
+        <v>6340450</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6463,22 +6444,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124795874</v>
+        <v>124796269</v>
       </c>
       <c r="B53" t="n">
-        <v>79004</v>
+        <v>5361</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6487,41 +6468,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1639</v>
+        <v>101728</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578029</v>
+        <v>578107</v>
       </c>
       <c r="R53" t="n">
-        <v>6340450</v>
+        <v>6340454</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6551,6 +6532,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6565,22 +6551,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124796269</v>
+        <v>124797132</v>
       </c>
       <c r="B54" t="n">
-        <v>5361</v>
+        <v>5196</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6589,25 +6575,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>101728</v>
+        <v>105930</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6617,10 +6603,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578107</v>
+        <v>578099</v>
       </c>
       <c r="R54" t="n">
-        <v>6340454</v>
+        <v>6340486</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6657,7 +6643,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Kläckhål</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6684,10 +6670,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124796060</v>
+        <v>124795874</v>
       </c>
       <c r="B55" t="n">
-        <v>79428</v>
+        <v>79004</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6696,38 +6682,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>1639</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578034</v>
+        <v>578029</v>
       </c>
       <c r="R55" t="n">
-        <v>6340457</v>
+        <v>6340450</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6786,10 +6772,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124797132</v>
+        <v>124797764</v>
       </c>
       <c r="B56" t="n">
-        <v>5196</v>
+        <v>57666</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6798,41 +6784,46 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578099</v>
+        <v>578056</v>
       </c>
       <c r="R56" t="n">
-        <v>6340486</v>
+        <v>6340468</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6862,11 +6853,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6886,17 +6872,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124796460</v>
+        <v>124796185</v>
       </c>
       <c r="B57" t="n">
-        <v>95423</v>
+        <v>79428</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6905,41 +6891,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2671</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578092</v>
+        <v>578013</v>
       </c>
       <c r="R57" t="n">
-        <v>6340465</v>
+        <v>6340449</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6983,12 +6969,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7097,10 +7083,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124796768</v>
+        <v>124796460</v>
       </c>
       <c r="B59" t="n">
-        <v>79428</v>
+        <v>95423</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7109,25 +7095,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>2671</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7137,10 +7123,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578118</v>
+        <v>578092</v>
       </c>
       <c r="R59" t="n">
-        <v>6340459</v>
+        <v>6340465</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7199,10 +7185,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124796606</v>
+        <v>124796060</v>
       </c>
       <c r="B60" t="n">
-        <v>92239</v>
+        <v>79428</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7211,41 +7197,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>26</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578096</v>
+        <v>578034</v>
       </c>
       <c r="R60" t="n">
-        <v>6340479</v>
+        <v>6340457</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7289,22 +7275,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124797831</v>
+        <v>124797648</v>
       </c>
       <c r="B61" t="n">
-        <v>96354</v>
+        <v>8447</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7313,25 +7299,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7341,10 +7327,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578055</v>
+        <v>578060</v>
       </c>
       <c r="R61" t="n">
-        <v>6340450</v>
+        <v>6340459</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7379,6 +7365,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Spår och kläckhål</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7396,17 +7387,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124796529</v>
+        <v>124796245</v>
       </c>
       <c r="B62" t="n">
-        <v>79891</v>
+        <v>79004</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7415,25 +7406,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>1639</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7443,10 +7434,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577974</v>
+        <v>577987</v>
       </c>
       <c r="R62" t="n">
-        <v>6340427</v>
+        <v>6340434</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7505,10 +7496,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124796306</v>
+        <v>124795668</v>
       </c>
       <c r="B63" t="n">
-        <v>79428</v>
+        <v>91023</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7517,38 +7508,42 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>1205</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577987</v>
+        <v>578042</v>
       </c>
       <c r="R63" t="n">
-        <v>6340434</v>
+        <v>6340382</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7607,10 +7602,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124796245</v>
+        <v>124797728</v>
       </c>
       <c r="B64" t="n">
-        <v>79004</v>
+        <v>57529</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7619,41 +7614,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1639</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>577987</v>
+        <v>578047</v>
       </c>
       <c r="R64" t="n">
-        <v>6340434</v>
+        <v>6340449</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7683,6 +7678,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7697,22 +7697,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124825657</v>
+        <v>124825691</v>
       </c>
       <c r="B65" t="n">
-        <v>92210</v>
+        <v>4772</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7721,30 +7721,32 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2075</v>
+        <v>100299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7752,10 +7754,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>577974</v>
+        <v>578135</v>
       </c>
       <c r="R65" t="n">
-        <v>6340399</v>
+        <v>6340398</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7788,6 +7790,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7815,10 +7822,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124825677</v>
+        <v>124825657</v>
       </c>
       <c r="B66" t="n">
-        <v>96390</v>
+        <v>92210</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7827,31 +7834,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2590</v>
+        <v>2075</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7859,10 +7865,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578131</v>
+        <v>577974</v>
       </c>
       <c r="R66" t="n">
-        <v>6340387</v>
+        <v>6340399</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7922,10 +7928,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124825691</v>
+        <v>124825677</v>
       </c>
       <c r="B67" t="n">
-        <v>4772</v>
+        <v>96390</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7938,28 +7944,27 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100299</v>
+        <v>2590</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7967,10 +7972,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>578135</v>
+        <v>578131</v>
       </c>
       <c r="R67" t="n">
-        <v>6340398</v>
+        <v>6340387</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8003,11 +8008,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -5529,10 +5529,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124795772</v>
+        <v>124796529</v>
       </c>
       <c r="B44" t="n">
-        <v>96354</v>
+        <v>80028</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5545,37 +5545,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578110</v>
+        <v>577974</v>
       </c>
       <c r="R44" t="n">
-        <v>6340428</v>
+        <v>6340427</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5619,22 +5619,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124795744</v>
+        <v>124795621</v>
       </c>
       <c r="B45" t="n">
-        <v>79428</v>
+        <v>58111</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5647,37 +5647,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>103018</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Mosse Hjortshult, Boda, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578042</v>
+        <v>578049</v>
       </c>
       <c r="R45" t="n">
-        <v>6340428</v>
+        <v>6340376</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5733,10 +5742,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124796529</v>
+        <v>124797764</v>
       </c>
       <c r="B46" t="n">
-        <v>79891</v>
+        <v>57793</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5749,37 +5758,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577974</v>
+        <v>578056</v>
       </c>
       <c r="R46" t="n">
-        <v>6340427</v>
+        <v>6340468</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5823,22 +5837,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124796306</v>
+        <v>124795772</v>
       </c>
       <c r="B47" t="n">
-        <v>79428</v>
+        <v>96522</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5851,37 +5865,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577987</v>
+        <v>578110</v>
       </c>
       <c r="R47" t="n">
-        <v>6340434</v>
+        <v>6340428</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5925,22 +5939,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124795621</v>
+        <v>124797728</v>
       </c>
       <c r="B48" t="n">
-        <v>57995</v>
+        <v>57632</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5953,46 +5967,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Boda, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578049</v>
+        <v>578047</v>
       </c>
       <c r="R48" t="n">
-        <v>6340376</v>
+        <v>6340449</v>
       </c>
       <c r="S48" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6022,6 +6027,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6036,22 +6046,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124796606</v>
+        <v>124796269</v>
       </c>
       <c r="B49" t="n">
-        <v>92239</v>
+        <v>5361</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6060,25 +6070,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>26</v>
+        <v>101728</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6088,10 +6098,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578096</v>
+        <v>578107</v>
       </c>
       <c r="R49" t="n">
-        <v>6340479</v>
+        <v>6340454</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6124,6 +6134,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6150,10 +6165,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124796768</v>
+        <v>124796060</v>
       </c>
       <c r="B50" t="n">
-        <v>79428</v>
+        <v>79565</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6186,17 +6201,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578118</v>
+        <v>578034</v>
       </c>
       <c r="R50" t="n">
-        <v>6340459</v>
+        <v>6340457</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6240,22 +6255,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124795887</v>
+        <v>124795668</v>
       </c>
       <c r="B51" t="n">
-        <v>96390</v>
+        <v>91177</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6268,37 +6283,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2590</v>
+        <v>1205</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578113</v>
+        <v>578042</v>
       </c>
       <c r="R51" t="n">
-        <v>6340445</v>
+        <v>6340382</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6342,22 +6361,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124797831</v>
+        <v>124795744</v>
       </c>
       <c r="B52" t="n">
-        <v>96354</v>
+        <v>79565</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6370,37 +6389,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578055</v>
+        <v>578042</v>
       </c>
       <c r="R52" t="n">
-        <v>6340450</v>
+        <v>6340428</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6444,22 +6463,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124796269</v>
+        <v>124797831</v>
       </c>
       <c r="B53" t="n">
-        <v>5361</v>
+        <v>96522</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6472,21 +6491,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>101728</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6496,10 +6515,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578107</v>
+        <v>578055</v>
       </c>
       <c r="R53" t="n">
-        <v>6340454</v>
+        <v>6340450</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6532,11 +6551,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6563,10 +6577,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124797132</v>
+        <v>124796606</v>
       </c>
       <c r="B54" t="n">
-        <v>5196</v>
+        <v>92394</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6579,21 +6593,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>105930</v>
+        <v>26</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6603,10 +6617,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578099</v>
+        <v>578096</v>
       </c>
       <c r="R54" t="n">
-        <v>6340486</v>
+        <v>6340479</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6639,11 +6653,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6670,10 +6679,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124795874</v>
+        <v>124795887</v>
       </c>
       <c r="B55" t="n">
-        <v>79004</v>
+        <v>96558</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6686,37 +6695,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1639</v>
+        <v>2590</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578029</v>
+        <v>578113</v>
       </c>
       <c r="R55" t="n">
-        <v>6340450</v>
+        <v>6340445</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6760,22 +6769,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124797764</v>
+        <v>124799230</v>
       </c>
       <c r="B56" t="n">
-        <v>57666</v>
+        <v>92365</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6788,42 +6797,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>2075</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578056</v>
+        <v>577970</v>
       </c>
       <c r="R56" t="n">
-        <v>6340468</v>
+        <v>6340397</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6867,22 +6871,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124796185</v>
+        <v>124797648</v>
       </c>
       <c r="B57" t="n">
-        <v>79428</v>
+        <v>8447</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6891,41 +6895,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578013</v>
+        <v>578060</v>
       </c>
       <c r="R57" t="n">
-        <v>6340449</v>
+        <v>6340459</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6955,6 +6959,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6969,22 +6978,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124799230</v>
+        <v>124796245</v>
       </c>
       <c r="B58" t="n">
-        <v>92210</v>
+        <v>79141</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6993,25 +7002,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2075</v>
+        <v>1639</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7021,10 +7030,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>577970</v>
+        <v>577987</v>
       </c>
       <c r="R58" t="n">
-        <v>6340397</v>
+        <v>6340434</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7083,10 +7092,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124796460</v>
+        <v>124795874</v>
       </c>
       <c r="B59" t="n">
-        <v>95423</v>
+        <v>79141</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7099,37 +7108,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2671</v>
+        <v>1639</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578092</v>
+        <v>578029</v>
       </c>
       <c r="R59" t="n">
-        <v>6340465</v>
+        <v>6340450</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7173,22 +7182,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124796060</v>
+        <v>124796768</v>
       </c>
       <c r="B60" t="n">
-        <v>79428</v>
+        <v>79565</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7221,17 +7230,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578034</v>
+        <v>578118</v>
       </c>
       <c r="R60" t="n">
-        <v>6340457</v>
+        <v>6340459</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7275,22 +7284,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124797648</v>
+        <v>124796460</v>
       </c>
       <c r="B61" t="n">
-        <v>8447</v>
+        <v>95591</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7303,21 +7312,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>2671</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7327,13 +7336,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578060</v>
+        <v>578092</v>
       </c>
       <c r="R61" t="n">
-        <v>6340459</v>
+        <v>6340465</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7363,11 +7372,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7387,17 +7391,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124796245</v>
+        <v>124796306</v>
       </c>
       <c r="B62" t="n">
-        <v>79004</v>
+        <v>79565</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7406,25 +7410,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1639</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7496,10 +7500,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124795668</v>
+        <v>124796185</v>
       </c>
       <c r="B63" t="n">
-        <v>91023</v>
+        <v>79565</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7508,42 +7512,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1205</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578042</v>
+        <v>578013</v>
       </c>
       <c r="R63" t="n">
-        <v>6340382</v>
+        <v>6340449</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7602,10 +7602,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124797728</v>
+        <v>124797132</v>
       </c>
       <c r="B64" t="n">
-        <v>57529</v>
+        <v>5196</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7614,20 +7614,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578047</v>
+        <v>578099</v>
       </c>
       <c r="R64" t="n">
-        <v>6340449</v>
+        <v>6340486</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7709,10 +7709,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124825691</v>
+        <v>124825657</v>
       </c>
       <c r="B65" t="n">
-        <v>4772</v>
+        <v>92365</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7721,32 +7721,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100299</v>
+        <v>2075</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7754,10 +7752,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>578135</v>
+        <v>577974</v>
       </c>
       <c r="R65" t="n">
-        <v>6340398</v>
+        <v>6340399</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7790,11 +7788,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7822,10 +7815,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124825657</v>
+        <v>124825691</v>
       </c>
       <c r="B66" t="n">
-        <v>92210</v>
+        <v>4772</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7834,30 +7827,32 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2075</v>
+        <v>100299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7865,10 +7860,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>577974</v>
+        <v>578135</v>
       </c>
       <c r="R66" t="n">
-        <v>6340399</v>
+        <v>6340398</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7901,6 +7896,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7931,7 +7931,7 @@
         <v>124825677</v>
       </c>
       <c r="B67" t="n">
-        <v>96390</v>
+        <v>96558</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -5742,10 +5742,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124797764</v>
+        <v>124795772</v>
       </c>
       <c r="B46" t="n">
-        <v>57793</v>
+        <v>96522</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5758,42 +5758,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578056</v>
+        <v>578110</v>
       </c>
       <c r="R46" t="n">
-        <v>6340468</v>
+        <v>6340428</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5849,10 +5844,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124795772</v>
+        <v>124797764</v>
       </c>
       <c r="B47" t="n">
-        <v>96522</v>
+        <v>57793</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5865,37 +5860,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578110</v>
+        <v>578056</v>
       </c>
       <c r="R47" t="n">
-        <v>6340428</v>
+        <v>6340468</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5951,10 +5951,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124797728</v>
+        <v>124796269</v>
       </c>
       <c r="B48" t="n">
-        <v>57632</v>
+        <v>5361</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578047</v>
+        <v>578107</v>
       </c>
       <c r="R48" t="n">
-        <v>6340449</v>
+        <v>6340454</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6058,10 +6058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124796269</v>
+        <v>124797728</v>
       </c>
       <c r="B49" t="n">
-        <v>5361</v>
+        <v>57632</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6074,21 +6074,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6098,10 +6098,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578107</v>
+        <v>578047</v>
       </c>
       <c r="R49" t="n">
-        <v>6340454</v>
+        <v>6340449</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Kläckhål</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7398,10 +7398,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124796306</v>
+        <v>124797132</v>
       </c>
       <c r="B62" t="n">
-        <v>79565</v>
+        <v>5196</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7410,41 +7410,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>105930</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577987</v>
+        <v>578099</v>
       </c>
       <c r="R62" t="n">
-        <v>6340434</v>
+        <v>6340486</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7474,6 +7474,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7488,19 +7493,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124796185</v>
+        <v>124796306</v>
       </c>
       <c r="B63" t="n">
         <v>79565</v>
@@ -7540,10 +7545,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578013</v>
+        <v>577987</v>
       </c>
       <c r="R63" t="n">
-        <v>6340449</v>
+        <v>6340434</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7602,10 +7607,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124797132</v>
+        <v>124796185</v>
       </c>
       <c r="B64" t="n">
-        <v>5196</v>
+        <v>79565</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7614,41 +7619,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>105930</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578099</v>
+        <v>578013</v>
       </c>
       <c r="R64" t="n">
-        <v>6340486</v>
+        <v>6340449</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7678,11 +7683,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7697,12 +7697,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -5529,10 +5529,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124796529</v>
+        <v>124795621</v>
       </c>
       <c r="B44" t="n">
-        <v>80028</v>
+        <v>58111</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5545,37 +5545,46 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>103018</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Mosse Hjortshult, Boda, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577974</v>
+        <v>578049</v>
       </c>
       <c r="R44" t="n">
-        <v>6340427</v>
+        <v>6340376</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5631,10 +5640,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124795621</v>
+        <v>124799230</v>
       </c>
       <c r="B45" t="n">
-        <v>58111</v>
+        <v>92365</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5647,46 +5656,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103018</v>
+        <v>2075</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Boidin</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Boda, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578049</v>
+        <v>577970</v>
       </c>
       <c r="R45" t="n">
-        <v>6340376</v>
+        <v>6340397</v>
       </c>
       <c r="S45" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5742,10 +5742,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124795772</v>
+        <v>124796245</v>
       </c>
       <c r="B46" t="n">
-        <v>96522</v>
+        <v>79141</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5754,41 +5754,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>1639</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578110</v>
+        <v>577987</v>
       </c>
       <c r="R46" t="n">
-        <v>6340428</v>
+        <v>6340434</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5832,22 +5832,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124797764</v>
+        <v>124796269</v>
       </c>
       <c r="B47" t="n">
-        <v>57793</v>
+        <v>5361</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5860,42 +5860,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>101728</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578056</v>
+        <v>578107</v>
       </c>
       <c r="R47" t="n">
-        <v>6340468</v>
+        <v>6340454</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5925,6 +5920,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5944,17 +5944,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124796269</v>
+        <v>124796060</v>
       </c>
       <c r="B48" t="n">
-        <v>5361</v>
+        <v>79565</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5967,37 +5967,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>101728</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578107</v>
+        <v>578034</v>
       </c>
       <c r="R48" t="n">
-        <v>6340454</v>
+        <v>6340457</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6027,11 +6027,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6046,22 +6041,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124797728</v>
+        <v>124795874</v>
       </c>
       <c r="B49" t="n">
-        <v>57632</v>
+        <v>79141</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6070,41 +6065,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>1639</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578047</v>
+        <v>578029</v>
       </c>
       <c r="R49" t="n">
-        <v>6340449</v>
+        <v>6340450</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6134,11 +6129,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6153,22 +6143,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124796060</v>
+        <v>124797764</v>
       </c>
       <c r="B50" t="n">
-        <v>79565</v>
+        <v>57793</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6181,37 +6171,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578034</v>
+        <v>578056</v>
       </c>
       <c r="R50" t="n">
-        <v>6340457</v>
+        <v>6340468</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6255,22 +6250,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124795668</v>
+        <v>124796768</v>
       </c>
       <c r="B51" t="n">
-        <v>91177</v>
+        <v>79565</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6279,45 +6274,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1205</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578042</v>
+        <v>578118</v>
       </c>
       <c r="R51" t="n">
-        <v>6340382</v>
+        <v>6340459</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6361,22 +6352,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124795744</v>
+        <v>124797648</v>
       </c>
       <c r="B52" t="n">
-        <v>79565</v>
+        <v>8447</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6385,41 +6376,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578042</v>
+        <v>578060</v>
       </c>
       <c r="R52" t="n">
-        <v>6340428</v>
+        <v>6340459</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6449,6 +6440,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6463,22 +6459,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124797831</v>
+        <v>124795744</v>
       </c>
       <c r="B53" t="n">
-        <v>96522</v>
+        <v>79565</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6491,37 +6487,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Norra Fagerhult, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578055</v>
+        <v>578042</v>
       </c>
       <c r="R53" t="n">
-        <v>6340450</v>
+        <v>6340428</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6565,22 +6561,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124796606</v>
+        <v>124797728</v>
       </c>
       <c r="B54" t="n">
-        <v>92394</v>
+        <v>57632</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6589,25 +6585,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>26</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6617,10 +6613,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578096</v>
+        <v>578047</v>
       </c>
       <c r="R54" t="n">
-        <v>6340479</v>
+        <v>6340449</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6653,6 +6649,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6781,10 +6782,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124799230</v>
+        <v>124795772</v>
       </c>
       <c r="B56" t="n">
-        <v>92365</v>
+        <v>96522</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6797,37 +6798,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2075</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>577970</v>
+        <v>578110</v>
       </c>
       <c r="R56" t="n">
-        <v>6340397</v>
+        <v>6340428</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6871,22 +6872,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124797648</v>
+        <v>124796460</v>
       </c>
       <c r="B57" t="n">
-        <v>8447</v>
+        <v>95591</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6899,21 +6900,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>2671</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6923,13 +6924,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578060</v>
+        <v>578092</v>
       </c>
       <c r="R57" t="n">
-        <v>6340459</v>
+        <v>6340465</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6959,11 +6960,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Spår och kläckhål</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6983,17 +6979,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124796245</v>
+        <v>124796606</v>
       </c>
       <c r="B58" t="n">
-        <v>79141</v>
+        <v>92394</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7006,37 +7002,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1639</v>
+        <v>26</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>577987</v>
+        <v>578096</v>
       </c>
       <c r="R58" t="n">
-        <v>6340434</v>
+        <v>6340479</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7080,22 +7076,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124795874</v>
+        <v>124796306</v>
       </c>
       <c r="B59" t="n">
-        <v>79141</v>
+        <v>79565</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7104,38 +7100,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1639</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hjortshult, Norra Fagerhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578029</v>
+        <v>577987</v>
       </c>
       <c r="R59" t="n">
-        <v>6340450</v>
+        <v>6340434</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7194,10 +7190,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124796768</v>
+        <v>124795668</v>
       </c>
       <c r="B60" t="n">
-        <v>79565</v>
+        <v>91177</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7206,41 +7202,45 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>1205</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Mosse Hjortshult, Mosse Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578118</v>
+        <v>578042</v>
       </c>
       <c r="R60" t="n">
-        <v>6340459</v>
+        <v>6340382</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7284,22 +7284,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124796460</v>
+        <v>124796529</v>
       </c>
       <c r="B61" t="n">
-        <v>95591</v>
+        <v>80028</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7308,41 +7308,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2671</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578092</v>
+        <v>577974</v>
       </c>
       <c r="R61" t="n">
-        <v>6340465</v>
+        <v>6340427</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7386,22 +7386,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124797132</v>
+        <v>124796185</v>
       </c>
       <c r="B62" t="n">
-        <v>5196</v>
+        <v>79565</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7410,41 +7410,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>105930</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gökhult, Gökhult, Sm</t>
+          <t>Hjortshult, Hjortshult, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578099</v>
+        <v>578013</v>
       </c>
       <c r="R62" t="n">
-        <v>6340486</v>
+        <v>6340449</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7474,11 +7474,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7493,22 +7488,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Gunnar Westling</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124796306</v>
+        <v>124797132</v>
       </c>
       <c r="B63" t="n">
-        <v>79565</v>
+        <v>5196</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7517,41 +7512,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>105930</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577987</v>
+        <v>578099</v>
       </c>
       <c r="R63" t="n">
-        <v>6340434</v>
+        <v>6340486</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7581,6 +7576,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7595,22 +7595,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124796185</v>
+        <v>124797831</v>
       </c>
       <c r="B64" t="n">
-        <v>79565</v>
+        <v>96522</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7623,37 +7623,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hjortshult, Hjortshult, Sm</t>
+          <t>Gökhult, Gökhult, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578013</v>
+        <v>578055</v>
       </c>
       <c r="R64" t="n">
-        <v>6340449</v>
+        <v>6340450</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7697,22 +7697,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad, Gunnar Westling</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124825657</v>
+        <v>124825677</v>
       </c>
       <c r="B65" t="n">
-        <v>92365</v>
+        <v>96558</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7721,30 +7721,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2075</v>
+        <v>2590</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7752,10 +7753,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>577974</v>
+        <v>578131</v>
       </c>
       <c r="R65" t="n">
-        <v>6340399</v>
+        <v>6340387</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7928,10 +7929,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124825677</v>
+        <v>124825657</v>
       </c>
       <c r="B67" t="n">
-        <v>96558</v>
+        <v>92365</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7940,31 +7941,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2590</v>
+        <v>2075</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7972,10 +7972,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>578131</v>
+        <v>577974</v>
       </c>
       <c r="R67" t="n">
-        <v>6340387</v>
+        <v>6340399</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>

--- a/artfynd/A 31665-2023 artfynd.xlsx
+++ b/artfynd/A 31665-2023 artfynd.xlsx
@@ -7714,11 +7714,6 @@
       <c r="B65" t="n">
         <v>96558</v>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>LC</t>
@@ -7816,44 +7811,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124825691</v>
+        <v>124825657</v>
       </c>
       <c r="B66" t="n">
-        <v>4772</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92365</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100299</v>
+        <v>2075</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7861,10 +7849,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578135</v>
+        <v>577974</v>
       </c>
       <c r="R66" t="n">
-        <v>6340398</v>
+        <v>6340399</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7897,11 +7885,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7929,42 +7912,39 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124825657</v>
+        <v>124825691</v>
       </c>
       <c r="B67" t="n">
-        <v>92365</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4772</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2075</v>
+        <v>100299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7972,10 +7952,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>577974</v>
+        <v>578135</v>
       </c>
       <c r="R67" t="n">
-        <v>6340399</v>
+        <v>6340398</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8008,6 +7988,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD67" t="b">
